--- a/data/template_output.xlsx
+++ b/data/template_output.xlsx
@@ -1525,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BU25"/>
+  <dimension ref="A2:BU26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2435,7 +2435,7 @@
       <c r="A15" s="39" t="n"/>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>9500887310</t>
+          <t>9500921816</t>
         </is>
       </c>
       <c r="C15" s="69" t="n"/>
@@ -2445,10 +2445,18 @@
       <c r="G15" s="41" t="n"/>
       <c r="H15" s="40" t="n"/>
       <c r="I15" s="42" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="41" t="n"/>
-      <c r="L15" s="41" t="n"/>
-      <c r="M15" s="44" t="n"/>
+      <c r="J15" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="41" t="n">
+        <v>16640</v>
+      </c>
+      <c r="L15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" s="44">
         <f>L15-M15</f>
         <v/>
@@ -2457,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="P15" s="41" t="n">
-        <v>0</v>
+        <v>29990</v>
       </c>
       <c r="Q15" s="41" t="n">
-        <v>46348.31</v>
+        <v>0</v>
       </c>
       <c r="R15" s="44" t="n">
         <v>0</v>
@@ -2470,93 +2478,109 @@
         <v/>
       </c>
       <c r="T15" s="46" t="n">
-        <v>-46348.31</v>
+        <v>0</v>
       </c>
       <c r="U15" s="41" t="n">
-        <v>0</v>
+        <v>53800</v>
       </c>
       <c r="V15" s="41" t="n">
-        <v>75000</v>
+        <v>153900</v>
       </c>
       <c r="W15" s="44" t="n">
-        <v>0</v>
+        <v>83104</v>
       </c>
       <c r="X15" s="53">
         <f>V15-W15</f>
         <v/>
       </c>
       <c r="Y15" s="46" t="n">
-        <v>-131233.16</v>
+        <v>-221467.43</v>
       </c>
       <c r="Z15" s="41" t="n">
-        <v>0</v>
+        <v>47200</v>
       </c>
       <c r="AA15" s="41" t="n">
-        <v>122899.16</v>
+        <v>114767.43</v>
       </c>
       <c r="AB15" s="44" t="n">
-        <v>99000</v>
+        <v>38880</v>
       </c>
       <c r="AC15" s="53">
         <f>AA15-AB15</f>
         <v/>
       </c>
       <c r="AD15" s="46" t="n">
-        <v>-122899.16</v>
+        <v>-185608.7</v>
       </c>
       <c r="AE15" s="41" t="n">
-        <v>0</v>
+        <v>47200</v>
       </c>
       <c r="AF15" s="41" t="n">
-        <v>82233.16</v>
+        <v>190808.7</v>
       </c>
       <c r="AG15" s="44" t="n">
-        <v>0</v>
+        <v>50320</v>
       </c>
       <c r="AH15" s="53">
         <f>AF15-AG15</f>
         <v/>
       </c>
       <c r="AI15" s="46" t="n">
-        <v>-26000</v>
+        <v>-201074.85</v>
       </c>
       <c r="AJ15" s="41" t="n">
-        <v>0</v>
+        <v>54280</v>
       </c>
       <c r="AK15" s="41" t="n">
-        <v>0</v>
+        <v>202954.85</v>
       </c>
       <c r="AL15" s="44" t="n">
-        <v>24333</v>
+        <v>59395</v>
       </c>
       <c r="AM15" s="53">
         <f>AK15-AL15</f>
         <v/>
       </c>
-      <c r="AN15" s="46" t="n"/>
-      <c r="AO15" s="41" t="n"/>
-      <c r="AP15" s="41" t="n"/>
-      <c r="AQ15" s="44" t="n"/>
+      <c r="AN15" s="46" t="n">
+        <v>-132113.58</v>
+      </c>
+      <c r="AO15" s="41" t="n">
+        <v>44840</v>
+      </c>
+      <c r="AP15" s="41" t="n">
+        <v>197906.01</v>
+      </c>
+      <c r="AQ15" s="44" t="n">
+        <v>40382.7</v>
+      </c>
       <c r="AR15" s="53">
         <f>AP15-AQ15</f>
         <v/>
       </c>
-      <c r="AS15" s="46" t="n"/>
-      <c r="AT15" s="41" t="n"/>
-      <c r="AU15" s="41" t="n"/>
-      <c r="AV15" s="44" t="n"/>
+      <c r="AS15" s="46" t="n">
+        <v>-199916</v>
+      </c>
+      <c r="AT15" s="41" t="n">
+        <v>47200</v>
+      </c>
+      <c r="AU15" s="41" t="n">
+        <v>127043.57</v>
+      </c>
+      <c r="AV15" s="44" t="n">
+        <v>52507.52</v>
+      </c>
       <c r="AW15" s="53">
         <f>AU15-AV15</f>
         <v/>
       </c>
       <c r="AX15" s="46" t="n">
-        <v>0</v>
+        <v>-127043.57</v>
       </c>
       <c r="AY15" s="41" t="n">
-        <v>0</v>
+        <v>56640</v>
       </c>
       <c r="AZ15" s="41" t="n">
-        <v>4497.19</v>
+        <v>79843.57000000001</v>
       </c>
       <c r="BA15" s="44" t="n">
         <v>0</v>
@@ -2565,26 +2589,50 @@
         <f>AZ15-BA15</f>
         <v/>
       </c>
-      <c r="BC15" s="46" t="n"/>
-      <c r="BD15" s="41" t="n"/>
-      <c r="BE15" s="41" t="n"/>
-      <c r="BF15" s="44" t="n"/>
+      <c r="BC15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="41" t="n">
+        <v>47200</v>
+      </c>
+      <c r="BE15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="BG15" s="53">
         <f>BE15-BF15</f>
         <v/>
       </c>
-      <c r="BH15" s="46" t="n"/>
-      <c r="BI15" s="41" t="n"/>
-      <c r="BJ15" s="41" t="n"/>
-      <c r="BK15" s="44" t="n"/>
+      <c r="BH15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="41" t="n">
+        <v>44840</v>
+      </c>
+      <c r="BJ15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="BL15" s="53">
         <f>BJ15-BK15</f>
         <v/>
       </c>
-      <c r="BM15" s="46" t="n"/>
-      <c r="BN15" s="41" t="n"/>
-      <c r="BO15" s="41" t="n"/>
-      <c r="BP15" s="44" t="n"/>
+      <c r="BM15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="41" t="n">
+        <v>55600</v>
+      </c>
+      <c r="BO15" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ15" s="53">
         <f>BO15-BP15</f>
         <v/>
@@ -2600,7 +2648,7 @@
       <c r="A16" s="47" t="n"/>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>9500879389</t>
+          <t>9501014469</t>
         </is>
       </c>
       <c r="C16" s="72" t="n"/>
@@ -2614,13 +2662,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="49" t="n">
-        <v>14535</v>
+        <v>0</v>
       </c>
       <c r="L16" s="49" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="52" t="n">
-        <v>13822.5</v>
+        <v>0</v>
       </c>
       <c r="N16" s="52">
         <f>L16-M16</f>
@@ -2630,106 +2678,106 @@
         <v>0</v>
       </c>
       <c r="P16" s="49" t="n">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="49" t="n">
-        <v>19385.28</v>
+        <v>0</v>
       </c>
       <c r="R16" s="52" t="n">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="S16" s="53">
         <f>Q16-R16</f>
         <v/>
       </c>
       <c r="T16" s="54" t="n">
-        <v>-19385.28</v>
+        <v>0</v>
       </c>
       <c r="U16" s="49" t="n">
-        <v>21375</v>
+        <v>0</v>
       </c>
       <c r="V16" s="49" t="n">
-        <v>22813.72</v>
+        <v>0</v>
       </c>
       <c r="W16" s="52" t="n">
-        <v>20425</v>
+        <v>0</v>
       </c>
       <c r="X16" s="53">
         <f>V16-W16</f>
         <v/>
       </c>
       <c r="Y16" s="54" t="n">
-        <v>-22813.72</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="49" t="n">
-        <v>15390</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="49" t="n">
-        <v>19294.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="49" t="n">
-        <v>15247.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="53">
         <f>AA16-AB16</f>
         <v/>
       </c>
       <c r="AD16" s="54" t="n">
-        <v>-19294.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="49" t="n">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="49" t="n">
-        <v>20952.78</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="49" t="n">
-        <v>11162.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="53">
         <f>AF16-AG16</f>
         <v/>
       </c>
       <c r="AI16" s="54" t="n">
-        <v>-20952.78</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="49" t="n">
-        <v>21375</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="49" t="n">
-        <v>30922.5</v>
+        <v>0</v>
       </c>
       <c r="AL16" s="49" t="n">
-        <v>16862.5</v>
+        <v>0</v>
       </c>
       <c r="AM16" s="53">
         <f>AK16-AL16</f>
         <v/>
       </c>
       <c r="AN16" s="54" t="n">
-        <v>-30922.5</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="49" t="n">
-        <v>855</v>
+        <v>36000</v>
       </c>
       <c r="AP16" s="49" t="n">
-        <v>14060</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="49" t="n">
-        <v>427.5</v>
+        <v>0</v>
       </c>
       <c r="AR16" s="53">
         <f>AP16-AQ16</f>
         <v/>
       </c>
       <c r="AS16" s="54" t="n">
-        <v>-14060</v>
+        <v>0</v>
       </c>
       <c r="AT16" s="49" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AU16" s="49" t="n">
-        <v>13632.5</v>
+        <v>0</v>
       </c>
       <c r="AV16" s="49" t="n">
         <v>0</v>
@@ -2739,13 +2787,13 @@
         <v/>
       </c>
       <c r="AX16" s="54" t="n">
-        <v>-13632.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" s="49" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AZ16" s="49" t="n">
-        <v>13632.5</v>
+        <v>0</v>
       </c>
       <c r="BA16" s="49" t="n">
         <v>0</v>
@@ -2758,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="BD16" s="49" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="BE16" s="49" t="n">
         <v>0</v>
@@ -2774,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="49" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="BJ16" s="49" t="n">
         <v>0</v>
@@ -2790,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="BN16" s="49" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="BO16" s="49" t="n">
         <v>0</v>
@@ -2813,7 +2861,7 @@
       <c r="A17" s="47" t="n"/>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>9500882917</t>
+          <t>9501014470</t>
         </is>
       </c>
       <c r="C17" s="72" t="n"/>
@@ -2827,13 +2875,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="56" t="n">
-        <v>38400</v>
+        <v>0</v>
       </c>
       <c r="L17" s="56" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="52" t="n">
-        <v>34040</v>
+        <v>0</v>
       </c>
       <c r="N17" s="52">
         <f>L17-M17</f>
@@ -2843,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="49" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="49" t="n">
-        <v>62210</v>
+        <v>0</v>
       </c>
       <c r="R17" s="52" t="n">
         <v>0</v>
@@ -2856,77 +2904,77 @@
         <v/>
       </c>
       <c r="T17" s="54" t="n">
-        <v>-78320</v>
+        <v>0</v>
       </c>
       <c r="U17" s="49" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="V17" s="49" t="n">
-        <v>121710</v>
+        <v>0</v>
       </c>
       <c r="W17" s="57" t="n">
-        <v>58648</v>
+        <v>0</v>
       </c>
       <c r="X17" s="53">
         <f>V17-W17</f>
         <v/>
       </c>
       <c r="Y17" s="54" t="n">
-        <v>-140172</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="56" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="56" t="n">
-        <v>128172</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="57" t="n">
-        <v>20960</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="53">
         <f>AA17-AB17</f>
         <v/>
       </c>
       <c r="AD17" s="54" t="n">
-        <v>-130564</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="56" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="56" t="n">
-        <v>158564</v>
+        <v>0</v>
       </c>
       <c r="AG17" s="57" t="n">
-        <v>102760</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="53">
         <f>AF17-AG17</f>
         <v/>
       </c>
       <c r="AI17" s="54" t="n">
-        <v>-140102</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="56" t="n">
-        <v>57600</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="56" t="n">
-        <v>117094</v>
+        <v>0</v>
       </c>
       <c r="AL17" s="57" t="n">
-        <v>38368</v>
+        <v>0</v>
       </c>
       <c r="AM17" s="53">
         <f>AK17-AL17</f>
         <v/>
       </c>
       <c r="AN17" s="54" t="n">
-        <v>-98592</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="56" t="n">
-        <v>2400</v>
+        <v>70183</v>
       </c>
       <c r="AP17" s="56" t="n">
-        <v>60224</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="57" t="n">
         <v>0</v>
@@ -2936,16 +2984,16 @@
         <v/>
       </c>
       <c r="AS17" s="54" t="n">
-        <v>-60224</v>
+        <v>0</v>
       </c>
       <c r="AT17" s="56" t="n">
-        <v>0</v>
+        <v>73470</v>
       </c>
       <c r="AU17" s="56" t="n">
         <v>0</v>
       </c>
       <c r="AV17" s="57" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="AW17" s="53">
         <f>AU17-AV17</f>
@@ -2955,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="AY17" s="56" t="n">
-        <v>0</v>
+        <v>92187.5</v>
       </c>
       <c r="AZ17" s="56" t="n">
-        <v>57824</v>
+        <v>0</v>
       </c>
       <c r="BA17" s="57" t="n">
         <v>0</v>
@@ -2971,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="BD17" s="56" t="n">
-        <v>0</v>
+        <v>72187.5</v>
       </c>
       <c r="BE17" s="56" t="n">
         <v>0</v>
@@ -2987,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="56" t="n">
-        <v>0</v>
+        <v>73470</v>
       </c>
       <c r="BJ17" s="56" t="n">
         <v>0</v>
@@ -3003,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="BN17" s="56" t="n">
-        <v>0</v>
+        <v>107926.5</v>
       </c>
       <c r="BO17" s="56" t="n">
         <v>0</v>
@@ -3024,7 +3072,11 @@
     </row>
     <row r="18">
       <c r="A18" s="47" t="n"/>
-      <c r="B18" s="48" t="n"/>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>9500887310</t>
+        </is>
+      </c>
       <c r="C18" s="72" t="n"/>
       <c r="D18" s="72" t="n"/>
       <c r="E18" s="48" t="n"/>
@@ -3040,42 +3092,82 @@
         <f>L18-M18</f>
         <v/>
       </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="49" t="n"/>
-      <c r="Q18" s="49" t="n"/>
-      <c r="R18" s="52" t="n"/>
+      <c r="O18" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="49" t="n">
+        <v>46348.31</v>
+      </c>
+      <c r="R18" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="S18" s="53">
         <f>Q18-R18</f>
         <v/>
       </c>
-      <c r="T18" s="54" t="n"/>
-      <c r="U18" s="49" t="n"/>
-      <c r="V18" s="49" t="n"/>
-      <c r="W18" s="52" t="n"/>
+      <c r="T18" s="54" t="n">
+        <v>-46348.31</v>
+      </c>
+      <c r="U18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="49" t="n">
+        <v>75000</v>
+      </c>
+      <c r="W18" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="X18" s="53">
         <f>V18-W18</f>
         <v/>
       </c>
-      <c r="Y18" s="54" t="n"/>
-      <c r="Z18" s="49" t="n"/>
-      <c r="AA18" s="49" t="n"/>
-      <c r="AB18" s="52" t="n"/>
+      <c r="Y18" s="54" t="n">
+        <v>-131233.16</v>
+      </c>
+      <c r="Z18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="49" t="n">
+        <v>122899.16</v>
+      </c>
+      <c r="AB18" s="52" t="n">
+        <v>99000</v>
+      </c>
       <c r="AC18" s="53">
         <f>AA18-AB18</f>
         <v/>
       </c>
-      <c r="AD18" s="54" t="n"/>
-      <c r="AE18" s="49" t="n"/>
-      <c r="AF18" s="49" t="n"/>
-      <c r="AG18" s="52" t="n"/>
+      <c r="AD18" s="54" t="n">
+        <v>-122899.16</v>
+      </c>
+      <c r="AE18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="49" t="n">
+        <v>82233.16</v>
+      </c>
+      <c r="AG18" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="AH18" s="53">
         <f>AF18-AG18</f>
         <v/>
       </c>
-      <c r="AI18" s="54" t="n"/>
-      <c r="AJ18" s="49" t="n"/>
-      <c r="AK18" s="49" t="n"/>
-      <c r="AL18" s="52" t="n"/>
+      <c r="AI18" s="54" t="n">
+        <v>-26000</v>
+      </c>
+      <c r="AJ18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="52" t="n">
+        <v>24333</v>
+      </c>
       <c r="AM18" s="53">
         <f>AK18-AL18</f>
         <v/>
@@ -3096,10 +3188,18 @@
         <f>AU18-AV18</f>
         <v/>
       </c>
-      <c r="AX18" s="54" t="n"/>
-      <c r="AY18" s="49" t="n"/>
-      <c r="AZ18" s="49" t="n"/>
-      <c r="BA18" s="52" t="n"/>
+      <c r="AX18" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="49" t="n">
+        <v>4497.19</v>
+      </c>
+      <c r="BA18" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="BB18" s="53">
         <f>AZ18-BA18</f>
         <v/>
@@ -3137,6 +3237,11 @@
     </row>
     <row r="19">
       <c r="A19" s="75" t="n"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>9500882917</t>
+        </is>
+      </c>
       <c r="C19" s="72" t="n"/>
       <c r="D19" s="72" t="n"/>
       <c r="E19" s="48" t="n"/>
@@ -3144,98 +3249,194 @@
       <c r="G19" s="49" t="n"/>
       <c r="H19" s="48" t="n"/>
       <c r="I19" s="50" t="n"/>
-      <c r="J19" s="51" t="n"/>
-      <c r="K19" s="49" t="n"/>
-      <c r="L19" s="49" t="n"/>
-      <c r="M19" s="52" t="n"/>
+      <c r="J19" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="49" t="n">
+        <v>38400</v>
+      </c>
+      <c r="L19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="52" t="n">
+        <v>34040</v>
+      </c>
       <c r="N19" s="52">
         <f>L19-M19</f>
         <v/>
       </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="49" t="n"/>
-      <c r="Q19" s="49" t="n"/>
-      <c r="R19" s="52" t="n"/>
+      <c r="O19" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="49" t="n">
+        <v>45600</v>
+      </c>
+      <c r="Q19" s="49" t="n">
+        <v>62210</v>
+      </c>
+      <c r="R19" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="S19" s="53">
         <f>Q19-R19</f>
         <v/>
       </c>
-      <c r="T19" s="54" t="n"/>
-      <c r="U19" s="49" t="n"/>
-      <c r="V19" s="49" t="n"/>
-      <c r="W19" s="52" t="n"/>
+      <c r="T19" s="54" t="n">
+        <v>-78320</v>
+      </c>
+      <c r="U19" s="49" t="n">
+        <v>60000</v>
+      </c>
+      <c r="V19" s="49" t="n">
+        <v>121710</v>
+      </c>
+      <c r="W19" s="52" t="n">
+        <v>58648</v>
+      </c>
       <c r="X19" s="53">
         <f>V19-W19</f>
         <v/>
       </c>
-      <c r="Y19" s="54" t="n"/>
-      <c r="Z19" s="49" t="n"/>
-      <c r="AA19" s="49" t="n"/>
-      <c r="AB19" s="49" t="n"/>
+      <c r="Y19" s="54" t="n">
+        <v>-140172</v>
+      </c>
+      <c r="Z19" s="49" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AA19" s="49" t="n">
+        <v>128172</v>
+      </c>
+      <c r="AB19" s="49" t="n">
+        <v>20960</v>
+      </c>
       <c r="AC19" s="53">
         <f>AA19-AB19</f>
         <v/>
       </c>
-      <c r="AD19" s="54" t="n"/>
-      <c r="AE19" s="49" t="n"/>
-      <c r="AF19" s="49" t="n"/>
-      <c r="AG19" s="49" t="n"/>
+      <c r="AD19" s="54" t="n">
+        <v>-130564</v>
+      </c>
+      <c r="AE19" s="49" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AF19" s="49" t="n">
+        <v>158564</v>
+      </c>
+      <c r="AG19" s="49" t="n">
+        <v>102760</v>
+      </c>
       <c r="AH19" s="53">
         <f>AF19-AG19</f>
         <v/>
       </c>
-      <c r="AI19" s="54" t="n"/>
-      <c r="AJ19" s="49" t="n"/>
-      <c r="AK19" s="49" t="n"/>
-      <c r="AL19" s="49" t="n"/>
+      <c r="AI19" s="54" t="n">
+        <v>-140102</v>
+      </c>
+      <c r="AJ19" s="49" t="n">
+        <v>57600</v>
+      </c>
+      <c r="AK19" s="49" t="n">
+        <v>117094</v>
+      </c>
+      <c r="AL19" s="49" t="n">
+        <v>38368</v>
+      </c>
       <c r="AM19" s="53">
         <f>AK19-AL19</f>
         <v/>
       </c>
-      <c r="AN19" s="54" t="n"/>
-      <c r="AO19" s="49" t="n"/>
-      <c r="AP19" s="49" t="n"/>
-      <c r="AQ19" s="49" t="n"/>
+      <c r="AN19" s="54" t="n">
+        <v>-98592</v>
+      </c>
+      <c r="AO19" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AP19" s="49" t="n">
+        <v>60224</v>
+      </c>
+      <c r="AQ19" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="AR19" s="53">
         <f>AP19-AQ19</f>
         <v/>
       </c>
-      <c r="AS19" s="54" t="n"/>
-      <c r="AT19" s="49" t="n"/>
-      <c r="AU19" s="49" t="n"/>
-      <c r="AV19" s="49" t="n"/>
+      <c r="AS19" s="54" t="n">
+        <v>-60224</v>
+      </c>
+      <c r="AT19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="49" t="n">
+        <v>2400</v>
+      </c>
       <c r="AW19" s="53">
         <f>AU19-AV19</f>
         <v/>
       </c>
-      <c r="AX19" s="54" t="n"/>
-      <c r="AY19" s="49" t="n"/>
-      <c r="AZ19" s="49" t="n"/>
-      <c r="BA19" s="49" t="n"/>
+      <c r="AX19" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="49" t="n">
+        <v>57824</v>
+      </c>
+      <c r="BA19" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="BB19" s="53">
         <f>AZ19-BA19</f>
         <v/>
       </c>
-      <c r="BC19" s="54" t="n"/>
-      <c r="BD19" s="49" t="n"/>
-      <c r="BE19" s="49" t="n"/>
-      <c r="BF19" s="49" t="n"/>
+      <c r="BC19" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="BG19" s="53">
         <f>BE19-BF19</f>
         <v/>
       </c>
-      <c r="BH19" s="54" t="n"/>
-      <c r="BI19" s="49" t="n"/>
-      <c r="BJ19" s="49" t="n"/>
-      <c r="BK19" s="49" t="n"/>
+      <c r="BH19" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="BL19" s="53">
         <f>BJ19-BK19</f>
         <v/>
       </c>
-      <c r="BM19" s="54" t="n"/>
-      <c r="BN19" s="49" t="n"/>
-      <c r="BO19" s="49" t="n"/>
-      <c r="BP19" s="49" t="n"/>
+      <c r="BM19" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ19" s="53">
         <f>BO19-BP19</f>
         <v/>
@@ -3249,7 +3450,11 @@
     </row>
     <row r="20">
       <c r="A20" s="47" t="n"/>
-      <c r="B20" s="48" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>9500879389</t>
+        </is>
+      </c>
       <c r="C20" s="72" t="n"/>
       <c r="D20" s="72" t="n"/>
       <c r="E20" s="48" t="n"/>
@@ -3257,98 +3462,194 @@
       <c r="G20" s="49" t="n"/>
       <c r="H20" s="48" t="n"/>
       <c r="I20" s="50" t="n"/>
-      <c r="J20" s="51" t="n"/>
-      <c r="K20" s="49" t="n"/>
-      <c r="L20" s="49" t="n"/>
-      <c r="M20" s="52" t="n"/>
+      <c r="J20" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="49" t="n">
+        <v>14535</v>
+      </c>
+      <c r="L20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="52" t="n">
+        <v>13822.5</v>
+      </c>
       <c r="N20" s="52">
         <f>L20-M20</f>
         <v/>
       </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="49" t="n"/>
-      <c r="Q20" s="49" t="n"/>
-      <c r="R20" s="52" t="n"/>
+      <c r="O20" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="49" t="n">
+        <v>17100</v>
+      </c>
+      <c r="Q20" s="49" t="n">
+        <v>19385.28</v>
+      </c>
+      <c r="R20" s="52" t="n">
+        <v>17100</v>
+      </c>
       <c r="S20" s="53">
         <f>Q20-R20</f>
         <v/>
       </c>
-      <c r="T20" s="54" t="n"/>
-      <c r="U20" s="49" t="n"/>
-      <c r="V20" s="49" t="n"/>
-      <c r="W20" s="52" t="n"/>
+      <c r="T20" s="54" t="n">
+        <v>-19385.28</v>
+      </c>
+      <c r="U20" s="49" t="n">
+        <v>21375</v>
+      </c>
+      <c r="V20" s="49" t="n">
+        <v>22813.72</v>
+      </c>
+      <c r="W20" s="52" t="n">
+        <v>20425</v>
+      </c>
       <c r="X20" s="53">
         <f>V20-W20</f>
         <v/>
       </c>
-      <c r="Y20" s="54" t="n"/>
-      <c r="Z20" s="49" t="n"/>
-      <c r="AA20" s="49" t="n"/>
-      <c r="AB20" s="52" t="n"/>
+      <c r="Y20" s="54" t="n">
+        <v>-22813.72</v>
+      </c>
+      <c r="Z20" s="49" t="n">
+        <v>15390</v>
+      </c>
+      <c r="AA20" s="49" t="n">
+        <v>19294.5</v>
+      </c>
+      <c r="AB20" s="52" t="n">
+        <v>15247.5</v>
+      </c>
       <c r="AC20" s="53">
         <f>AA20-AB20</f>
         <v/>
       </c>
-      <c r="AD20" s="54" t="n"/>
-      <c r="AE20" s="49" t="n"/>
-      <c r="AF20" s="49" t="n"/>
-      <c r="AG20" s="52" t="n"/>
+      <c r="AD20" s="54" t="n">
+        <v>-19294.5</v>
+      </c>
+      <c r="AE20" s="49" t="n">
+        <v>17100</v>
+      </c>
+      <c r="AF20" s="49" t="n">
+        <v>20952.78</v>
+      </c>
+      <c r="AG20" s="52" t="n">
+        <v>11162.5</v>
+      </c>
       <c r="AH20" s="53">
         <f>AF20-AG20</f>
         <v/>
       </c>
-      <c r="AI20" s="54" t="n"/>
-      <c r="AJ20" s="49" t="n"/>
-      <c r="AK20" s="49" t="n"/>
-      <c r="AL20" s="52" t="n"/>
+      <c r="AI20" s="54" t="n">
+        <v>-20952.78</v>
+      </c>
+      <c r="AJ20" s="49" t="n">
+        <v>21375</v>
+      </c>
+      <c r="AK20" s="49" t="n">
+        <v>30922.5</v>
+      </c>
+      <c r="AL20" s="52" t="n">
+        <v>16862.5</v>
+      </c>
       <c r="AM20" s="53">
         <f>AK20-AL20</f>
         <v/>
       </c>
-      <c r="AN20" s="54" t="n"/>
-      <c r="AO20" s="49" t="n"/>
-      <c r="AP20" s="49" t="n"/>
-      <c r="AQ20" s="52" t="n"/>
+      <c r="AN20" s="54" t="n">
+        <v>-30922.5</v>
+      </c>
+      <c r="AO20" s="49" t="n">
+        <v>855</v>
+      </c>
+      <c r="AP20" s="49" t="n">
+        <v>14060</v>
+      </c>
+      <c r="AQ20" s="52" t="n">
+        <v>427.5</v>
+      </c>
       <c r="AR20" s="53">
         <f>AP20-AQ20</f>
         <v/>
       </c>
-      <c r="AS20" s="54" t="n"/>
-      <c r="AT20" s="49" t="n"/>
-      <c r="AU20" s="49" t="n"/>
-      <c r="AV20" s="52" t="n"/>
+      <c r="AS20" s="54" t="n">
+        <v>-14060</v>
+      </c>
+      <c r="AT20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="49" t="n">
+        <v>13632.5</v>
+      </c>
+      <c r="AV20" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="AW20" s="53">
         <f>AU20-AV20</f>
         <v/>
       </c>
-      <c r="AX20" s="54" t="n"/>
-      <c r="AY20" s="49" t="n"/>
-      <c r="AZ20" s="49" t="n"/>
-      <c r="BA20" s="52" t="n"/>
+      <c r="AX20" s="54" t="n">
+        <v>-13632.5</v>
+      </c>
+      <c r="AY20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="49" t="n">
+        <v>13632.5</v>
+      </c>
+      <c r="BA20" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="BB20" s="53">
         <f>AZ20-BA20</f>
         <v/>
       </c>
-      <c r="BC20" s="54" t="n"/>
-      <c r="BD20" s="49" t="n"/>
-      <c r="BE20" s="49" t="n"/>
-      <c r="BF20" s="52" t="n"/>
+      <c r="BC20" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="BG20" s="53">
         <f>BE20-BF20</f>
         <v/>
       </c>
-      <c r="BH20" s="54" t="n"/>
-      <c r="BI20" s="49" t="n"/>
-      <c r="BJ20" s="49" t="n"/>
-      <c r="BK20" s="52" t="n"/>
+      <c r="BH20" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="BL20" s="53">
         <f>BJ20-BK20</f>
         <v/>
       </c>
-      <c r="BM20" s="54" t="n"/>
-      <c r="BN20" s="49" t="n"/>
-      <c r="BO20" s="49" t="n"/>
-      <c r="BP20" s="52" t="n"/>
+      <c r="BM20" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" s="52" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ20" s="53">
         <f>BO20-BP20</f>
         <v/>
@@ -3361,485 +3662,598 @@
       <c r="BT20" s="74" t="n"/>
     </row>
     <row r="21" customFormat="1" s="67">
-      <c r="A21" s="100" t="inlineStr">
-        <is>
-          <t>Previous Period Invoices</t>
-        </is>
-      </c>
-      <c r="B21" s="101" t="n"/>
-      <c r="C21" s="102" t="n"/>
-      <c r="D21" s="102" t="n"/>
-      <c r="E21" s="101" t="n"/>
-      <c r="F21" s="101" t="n"/>
-      <c r="G21" s="103" t="n"/>
-      <c r="H21" s="101" t="n"/>
-      <c r="I21" s="104" t="n"/>
-      <c r="J21" s="105" t="n"/>
-      <c r="K21" s="103" t="n"/>
-      <c r="L21" s="103" t="n"/>
-      <c r="M21" s="106" t="n"/>
-      <c r="N21" s="106">
-        <f>IF(OR(L21="",M21=""),"",L21-M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="105" t="n"/>
-      <c r="P21" s="103" t="n"/>
-      <c r="Q21" s="103" t="n"/>
-      <c r="R21" s="106" t="n"/>
-      <c r="S21" s="107" t="n"/>
-      <c r="T21" s="108" t="n"/>
-      <c r="U21" s="103" t="n"/>
-      <c r="V21" s="103" t="n"/>
-      <c r="W21" s="106" t="n"/>
-      <c r="X21" s="107" t="n"/>
-      <c r="Y21" s="108" t="n"/>
-      <c r="Z21" s="103" t="n"/>
-      <c r="AA21" s="103" t="n"/>
-      <c r="AB21" s="106" t="n"/>
-      <c r="AC21" s="107">
-        <f>IF(OR(AA21="",AB21=""),"",AA21-AB21)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="108" t="n"/>
-      <c r="AE21" s="103" t="n"/>
-      <c r="AF21" s="103" t="n"/>
-      <c r="AG21" s="106" t="n"/>
-      <c r="AH21" s="107">
-        <f>IF(OR(AF21="",AG21=""),"",AF21-AG21)</f>
-        <v/>
-      </c>
-      <c r="AI21" s="108" t="n"/>
-      <c r="AJ21" s="103" t="n"/>
-      <c r="AK21" s="103" t="n"/>
-      <c r="AL21" s="106" t="n"/>
-      <c r="AM21" s="107">
-        <f>IF(OR(AK21="",AL21=""),"",AK21-AL21)</f>
-        <v/>
-      </c>
-      <c r="AN21" s="108" t="n"/>
-      <c r="AO21" s="103" t="n"/>
-      <c r="AP21" s="103" t="n"/>
-      <c r="AQ21" s="106" t="n"/>
-      <c r="AR21" s="107">
-        <f>IF(OR(AP21="",AQ21=""),"",AP21-AQ21)</f>
-        <v/>
-      </c>
-      <c r="AS21" s="108" t="n"/>
-      <c r="AT21" s="103" t="n"/>
-      <c r="AU21" s="103" t="n"/>
-      <c r="AV21" s="106" t="n"/>
-      <c r="AW21" s="107">
-        <f>IF(OR(AU21="",AV21=""),"",AU21-AV21)</f>
-        <v/>
-      </c>
-      <c r="AX21" s="108" t="n"/>
-      <c r="AY21" s="103" t="n"/>
-      <c r="AZ21" s="103" t="n"/>
-      <c r="BA21" s="106" t="n"/>
-      <c r="BB21" s="107">
-        <f>IF(OR(AZ21="",BA21=""),"",AZ21-BA21)</f>
-        <v/>
-      </c>
-      <c r="BC21" s="108" t="n"/>
-      <c r="BD21" s="103" t="n"/>
-      <c r="BE21" s="103" t="n"/>
-      <c r="BF21" s="106" t="n"/>
-      <c r="BG21" s="107">
-        <f>IF(OR(BE21="",BF21=""),"",BE21-BF21)</f>
-        <v/>
-      </c>
-      <c r="BH21" s="108" t="n"/>
-      <c r="BI21" s="103" t="n"/>
-      <c r="BJ21" s="103" t="n"/>
-      <c r="BK21" s="106" t="n"/>
-      <c r="BL21" s="107">
-        <f>IF(OR(BJ21="",BK21=""),"",BJ21-BK21)</f>
-        <v/>
-      </c>
-      <c r="BM21" s="108" t="n"/>
-      <c r="BN21" s="103" t="n"/>
-      <c r="BO21" s="103" t="n"/>
-      <c r="BP21" s="106" t="n"/>
-      <c r="BQ21" s="107">
-        <f>IF(OR(BO21="",BP21=""),"",BO21-BP21)</f>
-        <v/>
-      </c>
-      <c r="BR21" s="105">
+      <c r="A21" s="47" t="n"/>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="72" t="n"/>
+      <c r="D21" s="72" t="n"/>
+      <c r="E21" s="48" t="n"/>
+      <c r="F21" s="48" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="48" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="51" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="52" t="n"/>
+      <c r="N21" s="52">
+        <f>L21-M21</f>
+        <v/>
+      </c>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="49" t="n"/>
+      <c r="R21" s="52" t="n"/>
+      <c r="S21" s="53">
+        <f>Q21-R21</f>
+        <v/>
+      </c>
+      <c r="T21" s="54" t="n"/>
+      <c r="U21" s="49" t="n"/>
+      <c r="V21" s="49" t="n"/>
+      <c r="W21" s="52" t="n"/>
+      <c r="X21" s="53">
+        <f>V21-W21</f>
+        <v/>
+      </c>
+      <c r="Y21" s="54" t="n"/>
+      <c r="Z21" s="49" t="n"/>
+      <c r="AA21" s="49" t="n"/>
+      <c r="AB21" s="52" t="n"/>
+      <c r="AC21" s="53">
+        <f>AA21-AB21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="54" t="n"/>
+      <c r="AE21" s="49" t="n"/>
+      <c r="AF21" s="49" t="n"/>
+      <c r="AG21" s="52" t="n"/>
+      <c r="AH21" s="53">
+        <f>AF21-AG21</f>
+        <v/>
+      </c>
+      <c r="AI21" s="54" t="n"/>
+      <c r="AJ21" s="49" t="n"/>
+      <c r="AK21" s="49" t="n"/>
+      <c r="AL21" s="52" t="n"/>
+      <c r="AM21" s="53">
+        <f>AK21-AL21</f>
+        <v/>
+      </c>
+      <c r="AN21" s="54" t="n"/>
+      <c r="AO21" s="49" t="n"/>
+      <c r="AP21" s="49" t="n"/>
+      <c r="AQ21" s="52" t="n"/>
+      <c r="AR21" s="53">
+        <f>AP21-AQ21</f>
+        <v/>
+      </c>
+      <c r="AS21" s="54" t="n"/>
+      <c r="AT21" s="49" t="n"/>
+      <c r="AU21" s="49" t="n"/>
+      <c r="AV21" s="52" t="n"/>
+      <c r="AW21" s="53">
+        <f>AU21-AV21</f>
+        <v/>
+      </c>
+      <c r="AX21" s="54" t="n"/>
+      <c r="AY21" s="49" t="n"/>
+      <c r="AZ21" s="49" t="n"/>
+      <c r="BA21" s="52" t="n"/>
+      <c r="BB21" s="53">
+        <f>AZ21-BA21</f>
+        <v/>
+      </c>
+      <c r="BC21" s="54" t="n"/>
+      <c r="BD21" s="49" t="n"/>
+      <c r="BE21" s="49" t="n"/>
+      <c r="BF21" s="52" t="n"/>
+      <c r="BG21" s="53">
+        <f>BE21-BF21</f>
+        <v/>
+      </c>
+      <c r="BH21" s="54" t="n"/>
+      <c r="BI21" s="49" t="n"/>
+      <c r="BJ21" s="49" t="n"/>
+      <c r="BK21" s="52" t="n"/>
+      <c r="BL21" s="53">
+        <f>BJ21-BK21</f>
+        <v/>
+      </c>
+      <c r="BM21" s="54" t="n"/>
+      <c r="BN21" s="49" t="n"/>
+      <c r="BO21" s="49" t="n"/>
+      <c r="BP21" s="52" t="n"/>
+      <c r="BQ21" s="53">
+        <f>BO21-BP21</f>
+        <v/>
+      </c>
+      <c r="BR21" s="51">
         <f>SUM(IF(M21&lt;&gt;"",M21,IF(L21&lt;&gt;"",L21,K21)),IF(R21&lt;&gt;"",R21,IF(Q21&lt;&gt;"",Q21,P21)),IF(W21&lt;&gt;"",W21,IF(V21&lt;&gt;"",V21,U21)),IF(AB21&lt;&gt;"",AB21,IF(AA21&lt;&gt;"",AA21,Z21)),IF(AG21&lt;&gt;"",AG21,IF(AF21&lt;&gt;"",AF21,AE21)),IF(AL21&lt;&gt;"",AL21,IF(AK21&lt;&gt;"",AK21,AJ21)),IF(AQ21&lt;&gt;"",AQ21,IF(AP21&lt;&gt;"",AP21,AO21)),IF(AV21&lt;&gt;"",AV21,IF(AU21&lt;&gt;"",AU21,AT21)),IF(BA21&lt;&gt;"",BA21,IF(AZ21&lt;&gt;"",AZ21,AY21)),IF(BF21&lt;&gt;"",BF21,IF(BE21&lt;&gt;"",BE21,BD21)),IF(BK21&lt;&gt;"",BK21,IF(BJ21&lt;&gt;"",BJ21,BI21)),IF(BP21&lt;&gt;"",BP21,IF(BO21&lt;&gt;"",BO21,BN21)))</f>
         <v/>
       </c>
-      <c r="BS21" s="109" t="n"/>
-      <c r="BT21" s="110" t="n"/>
+      <c r="BS21" s="73" t="n"/>
+      <c r="BT21" s="74" t="n"/>
     </row>
     <row r="22" customFormat="1" s="87">
-      <c r="A22" s="76" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="B22" s="77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="78" t="n"/>
-      <c r="D22" s="78" t="n"/>
-      <c r="E22" s="77" t="n"/>
-      <c r="F22" s="77" t="n"/>
-      <c r="G22" s="77" t="n"/>
-      <c r="H22" s="77" t="n"/>
-      <c r="I22" s="79" t="n"/>
-      <c r="J22" s="80" t="n"/>
-      <c r="K22" s="81" t="n"/>
-      <c r="L22" s="81" t="n"/>
-      <c r="M22" s="82" t="n"/>
-      <c r="N22" s="82">
-        <f>IF(OR(L22="",M22=""),"",L22-M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="80" t="n"/>
-      <c r="P22" s="81" t="n"/>
-      <c r="Q22" s="81" t="n"/>
-      <c r="R22" s="82" t="n"/>
-      <c r="S22" s="83">
-        <f>IF(OR(Q22="",R22=""),"",Q22-R22)</f>
-        <v/>
-      </c>
-      <c r="T22" s="84" t="n"/>
-      <c r="U22" s="81" t="n"/>
-      <c r="V22" s="81" t="n"/>
-      <c r="W22" s="82" t="n"/>
-      <c r="X22" s="83">
-        <f>IF(OR(V22="",W22=""),"",V22-W22)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="84" t="n"/>
-      <c r="Z22" s="81" t="n"/>
-      <c r="AA22" s="81" t="n"/>
-      <c r="AB22" s="82" t="n"/>
-      <c r="AC22" s="83">
-        <f>IF(OR(AA22="",AB22=""),"",AA22-AB22)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="84" t="n"/>
-      <c r="AE22" s="81" t="n"/>
-      <c r="AF22" s="81" t="n"/>
-      <c r="AG22" s="82" t="n"/>
-      <c r="AH22" s="83">
-        <f>IF(OR(AF22="",AG22=""),"",AF22-AG22)</f>
-        <v/>
-      </c>
-      <c r="AI22" s="84" t="n"/>
-      <c r="AJ22" s="81" t="n"/>
-      <c r="AK22" s="81" t="n"/>
-      <c r="AL22" s="82" t="n"/>
-      <c r="AM22" s="83">
-        <f>IF(OR(AK22="",AL22=""),"",AK22-AL22)</f>
-        <v/>
-      </c>
-      <c r="AN22" s="84" t="n"/>
-      <c r="AO22" s="81" t="n"/>
-      <c r="AP22" s="81" t="n"/>
-      <c r="AQ22" s="82" t="n"/>
-      <c r="AR22" s="83">
-        <f>IF(OR(AP22="",AQ22=""),"",AP22-AQ22)</f>
-        <v/>
-      </c>
-      <c r="AS22" s="84" t="n"/>
-      <c r="AT22" s="81" t="n"/>
-      <c r="AU22" s="81" t="n"/>
-      <c r="AV22" s="82" t="n"/>
-      <c r="AW22" s="83">
-        <f>IF(OR(AU22="",AV22=""),"",AU22-AV22)</f>
-        <v/>
-      </c>
-      <c r="AX22" s="84" t="n"/>
-      <c r="AY22" s="81" t="n"/>
-      <c r="AZ22" s="81" t="n"/>
-      <c r="BA22" s="82" t="n"/>
-      <c r="BB22" s="83">
-        <f>IF(OR(AZ22="",BA22=""),"",AZ22-BA22)</f>
-        <v/>
-      </c>
-      <c r="BC22" s="84" t="n"/>
-      <c r="BD22" s="81" t="n"/>
-      <c r="BE22" s="81" t="n"/>
-      <c r="BF22" s="82" t="n"/>
-      <c r="BG22" s="83">
-        <f>IF(OR(BE22="",BF22=""),"",BE22-BF22)</f>
-        <v/>
-      </c>
-      <c r="BH22" s="84" t="n"/>
-      <c r="BI22" s="81" t="n"/>
-      <c r="BJ22" s="81" t="n"/>
-      <c r="BK22" s="82" t="n"/>
-      <c r="BL22" s="83">
-        <f>IF(OR(BJ22="",BK22=""),"",BJ22-BK22)</f>
-        <v/>
-      </c>
-      <c r="BM22" s="84" t="n"/>
-      <c r="BN22" s="81" t="n"/>
-      <c r="BO22" s="81" t="n"/>
-      <c r="BP22" s="82" t="n"/>
-      <c r="BQ22" s="83">
-        <f>IF(OR(BO22="",BP22=""),"",BO22-BP22)</f>
-        <v/>
-      </c>
-      <c r="BR22" s="80">
-        <f>SUM(IF(M22&lt;&gt;"",M22,IF(L22&lt;&gt;"",L22,K22)),IF(R22&lt;&gt;"",R22,IF(Q22&lt;&gt;"",Q22,P22)),IF(W22&lt;&gt;"",W22,IF(V22&lt;&gt;"",V22,U22)),IF(AB22&lt;&gt;"",AB22,IF(AA22&lt;&gt;"",AA22,Z22)),IF(AG22&lt;&gt;"",AG22,IF(AF22&lt;&gt;"",AF22,AE22)),IF(AL22&lt;&gt;"",AL22,IF(AK22&lt;&gt;"",AK22,AJ22)),IF(AQ22&lt;&gt;"",AQ22,IF(AP22&lt;&gt;"",AP22,AO22)),IF(AV22&lt;&gt;"",AV22,IF(AU22&lt;&gt;"",AU22,AT22)),IF(BA22&lt;&gt;"",BA22,IF(AZ22&lt;&gt;"",AZ22,AY22)),IF(BF22&lt;&gt;"",BF22,IF(BE22&lt;&gt;"",BE22,BD22)),IF(BK22&lt;&gt;"",BK22,IF(BJ22&lt;&gt;"",BJ22,BI22)),IF(BP22&lt;&gt;"",BP22,IF(BO22&lt;&gt;"",BO22,BN22)))</f>
-        <v/>
-      </c>
-      <c r="BS22" s="85" t="n"/>
-      <c r="BT22" s="86" t="n"/>
+      <c r="A22" s="100" t="inlineStr">
+        <is>
+          <t>Previous Period Invoices</t>
+        </is>
+      </c>
+      <c r="B22" s="101" t="n"/>
+      <c r="C22" s="102" t="n"/>
+      <c r="D22" s="102" t="n"/>
+      <c r="E22" s="101" t="n"/>
+      <c r="F22" s="101" t="n"/>
+      <c r="G22" s="103" t="n"/>
+      <c r="H22" s="101" t="n"/>
+      <c r="I22" s="104" t="n"/>
+      <c r="J22" s="105" t="n"/>
+      <c r="K22" s="103" t="n"/>
+      <c r="L22" s="103" t="n"/>
+      <c r="M22" s="106" t="n"/>
+      <c r="N22" s="106">
+        <f>IF(OR(L21="",M21=""),"",L21-M21)</f>
+        <v/>
+      </c>
+      <c r="O22" s="105" t="n"/>
+      <c r="P22" s="103" t="n"/>
+      <c r="Q22" s="103" t="n"/>
+      <c r="R22" s="106" t="n"/>
+      <c r="S22" s="107" t="n"/>
+      <c r="T22" s="108" t="n"/>
+      <c r="U22" s="103" t="n"/>
+      <c r="V22" s="103" t="n"/>
+      <c r="W22" s="106" t="n"/>
+      <c r="X22" s="107" t="n"/>
+      <c r="Y22" s="108" t="n"/>
+      <c r="Z22" s="103" t="n"/>
+      <c r="AA22" s="103" t="n"/>
+      <c r="AB22" s="106" t="n"/>
+      <c r="AC22" s="107">
+        <f>IF(OR(AA21="",AB21=""),"",AA21-AB21)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="108" t="n"/>
+      <c r="AE22" s="103" t="n"/>
+      <c r="AF22" s="103" t="n"/>
+      <c r="AG22" s="106" t="n"/>
+      <c r="AH22" s="107">
+        <f>IF(OR(AF21="",AG21=""),"",AF21-AG21)</f>
+        <v/>
+      </c>
+      <c r="AI22" s="108" t="n"/>
+      <c r="AJ22" s="103" t="n"/>
+      <c r="AK22" s="103" t="n"/>
+      <c r="AL22" s="106" t="n"/>
+      <c r="AM22" s="107">
+        <f>IF(OR(AK21="",AL21=""),"",AK21-AL21)</f>
+        <v/>
+      </c>
+      <c r="AN22" s="108" t="n"/>
+      <c r="AO22" s="103" t="n"/>
+      <c r="AP22" s="103" t="n"/>
+      <c r="AQ22" s="106" t="n"/>
+      <c r="AR22" s="107">
+        <f>IF(OR(AP21="",AQ21=""),"",AP21-AQ21)</f>
+        <v/>
+      </c>
+      <c r="AS22" s="108" t="n"/>
+      <c r="AT22" s="103" t="n"/>
+      <c r="AU22" s="103" t="n"/>
+      <c r="AV22" s="106" t="n"/>
+      <c r="AW22" s="107">
+        <f>IF(OR(AU21="",AV21=""),"",AU21-AV21)</f>
+        <v/>
+      </c>
+      <c r="AX22" s="108" t="n"/>
+      <c r="AY22" s="103" t="n"/>
+      <c r="AZ22" s="103" t="n"/>
+      <c r="BA22" s="106" t="n"/>
+      <c r="BB22" s="107">
+        <f>IF(OR(AZ21="",BA21=""),"",AZ21-BA21)</f>
+        <v/>
+      </c>
+      <c r="BC22" s="108" t="n"/>
+      <c r="BD22" s="103" t="n"/>
+      <c r="BE22" s="103" t="n"/>
+      <c r="BF22" s="106" t="n"/>
+      <c r="BG22" s="107">
+        <f>IF(OR(BE21="",BF21=""),"",BE21-BF21)</f>
+        <v/>
+      </c>
+      <c r="BH22" s="108" t="n"/>
+      <c r="BI22" s="103" t="n"/>
+      <c r="BJ22" s="103" t="n"/>
+      <c r="BK22" s="106" t="n"/>
+      <c r="BL22" s="107">
+        <f>IF(OR(BJ21="",BK21=""),"",BJ21-BK21)</f>
+        <v/>
+      </c>
+      <c r="BM22" s="108" t="n"/>
+      <c r="BN22" s="103" t="n"/>
+      <c r="BO22" s="103" t="n"/>
+      <c r="BP22" s="106" t="n"/>
+      <c r="BQ22" s="107">
+        <f>IF(OR(BO21="",BP21=""),"",BO21-BP21)</f>
+        <v/>
+      </c>
+      <c r="BR22" s="105">
+        <f>SUM(IF(M21&lt;&gt;"",M21,IF(L21&lt;&gt;"",L21,K21)),IF(R21&lt;&gt;"",R21,IF(Q21&lt;&gt;"",Q21,P21)),IF(W21&lt;&gt;"",W21,IF(V21&lt;&gt;"",V21,U21)),IF(AB21&lt;&gt;"",AB21,IF(AA21&lt;&gt;"",AA21,Z21)),IF(AG21&lt;&gt;"",AG21,IF(AF21&lt;&gt;"",AF21,AE21)),IF(AL21&lt;&gt;"",AL21,IF(AK21&lt;&gt;"",AK21,AJ21)),IF(AQ21&lt;&gt;"",AQ21,IF(AP21&lt;&gt;"",AP21,AO21)),IF(AV21&lt;&gt;"",AV21,IF(AU21&lt;&gt;"",AU21,AT21)),IF(BA21&lt;&gt;"",BA21,IF(AZ21&lt;&gt;"",AZ21,AY21)),IF(BF21&lt;&gt;"",BF21,IF(BE21&lt;&gt;"",BE21,BD21)),IF(BK21&lt;&gt;"",BK21,IF(BJ21&lt;&gt;"",BJ21,BI21)),IF(BP21&lt;&gt;"",BP21,IF(BO21&lt;&gt;"",BO21,BN21)))</f>
+        <v/>
+      </c>
+      <c r="BS22" s="109" t="n"/>
+      <c r="BT22" s="110" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="88" t="n"/>
-      <c r="B23" s="89" t="n"/>
-      <c r="C23" s="90" t="n"/>
-      <c r="D23" s="90" t="n"/>
-      <c r="E23" s="89" t="n"/>
-      <c r="F23" s="89" t="n"/>
-      <c r="G23" s="89" t="n"/>
-      <c r="H23" s="89" t="n"/>
-      <c r="I23" s="91" t="n"/>
-      <c r="J23" s="92" t="n"/>
-      <c r="K23" s="93" t="n"/>
-      <c r="L23" s="93" t="n"/>
-      <c r="M23" s="52" t="n"/>
-      <c r="N23" s="52">
-        <f>IF(OR(L23="",M23=""),"",L23-M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="92" t="n"/>
-      <c r="P23" s="93" t="n"/>
-      <c r="Q23" s="93" t="n"/>
-      <c r="R23" s="52" t="n"/>
-      <c r="S23" s="53">
-        <f>IF(OR(Q23="",R23=""),"",Q23-R23)</f>
-        <v/>
-      </c>
-      <c r="T23" s="58" t="n"/>
-      <c r="U23" s="93" t="n"/>
-      <c r="V23" s="93" t="n"/>
-      <c r="W23" s="52" t="n"/>
-      <c r="X23" s="53">
-        <f>IF(OR(V23="",W23=""),"",V23-W23)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="58" t="n"/>
-      <c r="Z23" s="93" t="n"/>
-      <c r="AA23" s="93" t="n"/>
-      <c r="AB23" s="52" t="n"/>
-      <c r="AC23" s="53">
-        <f>IF(OR(AA23="",AB23=""),"",AA23-AB23)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="58" t="n"/>
-      <c r="AE23" s="93" t="n"/>
-      <c r="AF23" s="93" t="n"/>
-      <c r="AG23" s="52" t="n"/>
-      <c r="AH23" s="53">
-        <f>IF(OR(AF23="",AG23=""),"",AF23-AG23)</f>
-        <v/>
-      </c>
-      <c r="AI23" s="58" t="n"/>
-      <c r="AJ23" s="93" t="n"/>
-      <c r="AK23" s="93" t="n"/>
-      <c r="AL23" s="52" t="n"/>
-      <c r="AM23" s="53">
-        <f>IF(OR(AK23="",AL23=""),"",AK23-AL23)</f>
-        <v/>
-      </c>
-      <c r="AN23" s="58" t="n"/>
-      <c r="AO23" s="93" t="n"/>
-      <c r="AP23" s="93" t="n"/>
-      <c r="AQ23" s="52" t="n"/>
-      <c r="AR23" s="53">
-        <f>IF(OR(AP23="",AQ23=""),"",AP23-AQ23)</f>
-        <v/>
-      </c>
-      <c r="AS23" s="58" t="n"/>
-      <c r="AT23" s="93" t="n"/>
-      <c r="AU23" s="93" t="n"/>
-      <c r="AV23" s="52" t="n"/>
-      <c r="AW23" s="53">
-        <f>IF(OR(AU23="",AV23=""),"",AU23-AV23)</f>
-        <v/>
-      </c>
-      <c r="AX23" s="58" t="n"/>
-      <c r="AY23" s="93" t="n"/>
-      <c r="AZ23" s="93" t="n"/>
-      <c r="BA23" s="52" t="n"/>
-      <c r="BB23" s="53">
-        <f>IF(OR(AZ23="",BA23=""),"",AZ23-BA23)</f>
-        <v/>
-      </c>
-      <c r="BC23" s="58" t="n"/>
-      <c r="BD23" s="93" t="n"/>
-      <c r="BE23" s="93" t="n"/>
-      <c r="BF23" s="52" t="n"/>
-      <c r="BG23" s="53">
-        <f>IF(OR(BE23="",BF23=""),"",BE23-BF23)</f>
-        <v/>
-      </c>
-      <c r="BH23" s="58" t="n"/>
-      <c r="BI23" s="93" t="n"/>
-      <c r="BJ23" s="93" t="n"/>
-      <c r="BK23" s="52" t="n"/>
-      <c r="BL23" s="53">
-        <f>IF(OR(BJ23="",BK23=""),"",BJ23-BK23)</f>
-        <v/>
-      </c>
-      <c r="BM23" s="58" t="n"/>
-      <c r="BN23" s="93" t="n"/>
-      <c r="BO23" s="93" t="n"/>
-      <c r="BP23" s="52" t="n"/>
-      <c r="BQ23" s="53">
-        <f>IF(OR(BO23="",BP23=""),"",BO23-BP23)</f>
-        <v/>
-      </c>
-      <c r="BR23" s="51">
-        <f>SUM(IF(M23&lt;&gt;"",M23,IF(L23&lt;&gt;"",L23,K23)),IF(R23&lt;&gt;"",R23,IF(Q23&lt;&gt;"",Q23,P23)),IF(W23&lt;&gt;"",W23,IF(V23&lt;&gt;"",V23,U23)),IF(AB23&lt;&gt;"",AB23,IF(AA23&lt;&gt;"",AA23,Z23)),IF(AG23&lt;&gt;"",AG23,IF(AF23&lt;&gt;"",AF23,AE23)),IF(AL23&lt;&gt;"",AL23,IF(AK23&lt;&gt;"",AK23,AJ23)),IF(AQ23&lt;&gt;"",AQ23,IF(AP23&lt;&gt;"",AP23,AO23)),IF(AV23&lt;&gt;"",AV23,IF(AU23&lt;&gt;"",AU23,AT23)),IF(BA23&lt;&gt;"",BA23,IF(AZ23&lt;&gt;"",AZ23,AY23)),IF(BF23&lt;&gt;"",BF23,IF(BE23&lt;&gt;"",BE23,BD23)),IF(BK23&lt;&gt;"",BK23,IF(BJ23&lt;&gt;"",BJ23,BI23)),IF(BP23&lt;&gt;"",BP23,IF(BO23&lt;&gt;"",BO23,BN23)))</f>
-        <v/>
-      </c>
-      <c r="BS23" s="94" t="n"/>
-      <c r="BT23" s="95" t="n"/>
+      <c r="A23" s="76" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B23" s="77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="78" t="n"/>
+      <c r="D23" s="78" t="n"/>
+      <c r="E23" s="77" t="n"/>
+      <c r="F23" s="77" t="n"/>
+      <c r="G23" s="77" t="n"/>
+      <c r="H23" s="77" t="n"/>
+      <c r="I23" s="79" t="n"/>
+      <c r="J23" s="80" t="n"/>
+      <c r="K23" s="81" t="n"/>
+      <c r="L23" s="81" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82">
+        <f>IF(OR(L22="",M22=""),"",L22-M22)</f>
+        <v/>
+      </c>
+      <c r="O23" s="80" t="n"/>
+      <c r="P23" s="81" t="n"/>
+      <c r="Q23" s="81" t="n"/>
+      <c r="R23" s="82" t="n"/>
+      <c r="S23" s="83">
+        <f>IF(OR(Q22="",R22=""),"",Q22-R22)</f>
+        <v/>
+      </c>
+      <c r="T23" s="84" t="n"/>
+      <c r="U23" s="81" t="n"/>
+      <c r="V23" s="81" t="n"/>
+      <c r="W23" s="82" t="n"/>
+      <c r="X23" s="83">
+        <f>IF(OR(V22="",W22=""),"",V22-W22)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="84" t="n"/>
+      <c r="Z23" s="81" t="n"/>
+      <c r="AA23" s="81" t="n"/>
+      <c r="AB23" s="82" t="n"/>
+      <c r="AC23" s="83">
+        <f>IF(OR(AA22="",AB22=""),"",AA22-AB22)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="84" t="n"/>
+      <c r="AE23" s="81" t="n"/>
+      <c r="AF23" s="81" t="n"/>
+      <c r="AG23" s="82" t="n"/>
+      <c r="AH23" s="83">
+        <f>IF(OR(AF22="",AG22=""),"",AF22-AG22)</f>
+        <v/>
+      </c>
+      <c r="AI23" s="84" t="n"/>
+      <c r="AJ23" s="81" t="n"/>
+      <c r="AK23" s="81" t="n"/>
+      <c r="AL23" s="82" t="n"/>
+      <c r="AM23" s="83">
+        <f>IF(OR(AK22="",AL22=""),"",AK22-AL22)</f>
+        <v/>
+      </c>
+      <c r="AN23" s="84" t="n"/>
+      <c r="AO23" s="81" t="n"/>
+      <c r="AP23" s="81" t="n"/>
+      <c r="AQ23" s="82" t="n"/>
+      <c r="AR23" s="83">
+        <f>IF(OR(AP22="",AQ22=""),"",AP22-AQ22)</f>
+        <v/>
+      </c>
+      <c r="AS23" s="84" t="n"/>
+      <c r="AT23" s="81" t="n"/>
+      <c r="AU23" s="81" t="n"/>
+      <c r="AV23" s="82" t="n"/>
+      <c r="AW23" s="83">
+        <f>IF(OR(AU22="",AV22=""),"",AU22-AV22)</f>
+        <v/>
+      </c>
+      <c r="AX23" s="84" t="n"/>
+      <c r="AY23" s="81" t="n"/>
+      <c r="AZ23" s="81" t="n"/>
+      <c r="BA23" s="82" t="n"/>
+      <c r="BB23" s="83">
+        <f>IF(OR(AZ22="",BA22=""),"",AZ22-BA22)</f>
+        <v/>
+      </c>
+      <c r="BC23" s="84" t="n"/>
+      <c r="BD23" s="81" t="n"/>
+      <c r="BE23" s="81" t="n"/>
+      <c r="BF23" s="82" t="n"/>
+      <c r="BG23" s="83">
+        <f>IF(OR(BE22="",BF22=""),"",BE22-BF22)</f>
+        <v/>
+      </c>
+      <c r="BH23" s="84" t="n"/>
+      <c r="BI23" s="81" t="n"/>
+      <c r="BJ23" s="81" t="n"/>
+      <c r="BK23" s="82" t="n"/>
+      <c r="BL23" s="83">
+        <f>IF(OR(BJ22="",BK22=""),"",BJ22-BK22)</f>
+        <v/>
+      </c>
+      <c r="BM23" s="84" t="n"/>
+      <c r="BN23" s="81" t="n"/>
+      <c r="BO23" s="81" t="n"/>
+      <c r="BP23" s="82" t="n"/>
+      <c r="BQ23" s="83">
+        <f>IF(OR(BO22="",BP22=""),"",BO22-BP22)</f>
+        <v/>
+      </c>
+      <c r="BR23" s="80">
+        <f>SUM(IF(M22&lt;&gt;"",M22,IF(L22&lt;&gt;"",L22,K22)),IF(R22&lt;&gt;"",R22,IF(Q22&lt;&gt;"",Q22,P22)),IF(W22&lt;&gt;"",W22,IF(V22&lt;&gt;"",V22,U22)),IF(AB22&lt;&gt;"",AB22,IF(AA22&lt;&gt;"",AA22,Z22)),IF(AG22&lt;&gt;"",AG22,IF(AF22&lt;&gt;"",AF22,AE22)),IF(AL22&lt;&gt;"",AL22,IF(AK22&lt;&gt;"",AK22,AJ22)),IF(AQ22&lt;&gt;"",AQ22,IF(AP22&lt;&gt;"",AP22,AO22)),IF(AV22&lt;&gt;"",AV22,IF(AU22&lt;&gt;"",AU22,AT22)),IF(BA22&lt;&gt;"",BA22,IF(AZ22&lt;&gt;"",AZ22,AY22)),IF(BF22&lt;&gt;"",BF22,IF(BE22&lt;&gt;"",BE22,BD22)),IF(BK22&lt;&gt;"",BK22,IF(BJ22&lt;&gt;"",BJ22,BI22)),IF(BP22&lt;&gt;"",BP22,IF(BO22&lt;&gt;"",BO22,BN22)))</f>
+        <v/>
+      </c>
+      <c r="BS23" s="85" t="n"/>
+      <c r="BT23" s="86" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A24" s="59" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="B24" s="60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="96" t="n"/>
-      <c r="D24" s="96" t="n"/>
-      <c r="E24" s="60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="60" t="n"/>
-      <c r="G24" s="60" t="n"/>
-      <c r="H24" s="60" t="n"/>
-      <c r="I24" s="61" t="n"/>
-      <c r="J24" s="66" t="n"/>
-      <c r="K24" s="62" t="n"/>
-      <c r="L24" s="62" t="n"/>
-      <c r="M24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=1,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="N24" s="97">
-        <f>IF(OR(L24="",M24=""),"",L24-M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="66" t="n"/>
-      <c r="P24" s="62" t="n"/>
-      <c r="Q24" s="62" t="n"/>
-      <c r="R24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=2,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="65" t="n"/>
-      <c r="U24" s="62" t="n"/>
-      <c r="V24" s="62" t="n"/>
-      <c r="W24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=3,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="X24" s="64" t="n"/>
-      <c r="Y24" s="65" t="n"/>
-      <c r="Z24" s="62" t="n"/>
-      <c r="AA24" s="62" t="n"/>
-      <c r="AB24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=4,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="AC24" s="64" t="n"/>
-      <c r="AD24" s="65" t="n"/>
-      <c r="AE24" s="62" t="n"/>
-      <c r="AF24" s="62" t="n"/>
-      <c r="AG24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=5,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="AH24" s="64" t="n"/>
-      <c r="AI24" s="65" t="n"/>
-      <c r="AJ24" s="62" t="n"/>
-      <c r="AK24" s="62" t="n"/>
-      <c r="AL24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=6,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="AM24" s="64" t="n"/>
-      <c r="AN24" s="65" t="n"/>
-      <c r="AO24" s="62" t="n"/>
-      <c r="AP24" s="62" t="n"/>
-      <c r="AQ24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=7,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="AR24" s="64" t="n"/>
-      <c r="AS24" s="65" t="n"/>
-      <c r="AT24" s="62" t="n"/>
-      <c r="AU24" s="62" t="n"/>
-      <c r="AV24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=8,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="AW24" s="64" t="n"/>
-      <c r="AX24" s="65" t="n"/>
-      <c r="AY24" s="62" t="n"/>
-      <c r="AZ24" s="62" t="n"/>
-      <c r="BA24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=9,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="BB24" s="64" t="n"/>
-      <c r="BC24" s="65" t="n"/>
-      <c r="BD24" s="62" t="n"/>
-      <c r="BE24" s="62" t="n"/>
-      <c r="BF24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=10,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
-        <v/>
-      </c>
-      <c r="BG24" s="64" t="n"/>
-      <c r="BH24" s="65" t="n"/>
-      <c r="BI24" s="62" t="n"/>
-      <c r="BJ24" s="62" t="n"/>
-      <c r="BK24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;=11,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),IF(MONTH(TODAY())=11,($BS$13-$BR$13)/2,0))</f>
-        <v/>
-      </c>
-      <c r="BL24" s="64" t="n"/>
-      <c r="BM24" s="65" t="n"/>
-      <c r="BN24" s="62" t="n"/>
-      <c r="BO24" s="62" t="n"/>
-      <c r="BP24" s="63">
-        <f>IF((MONTH(TODAY()) + 2)&lt;12,($BS$13-$BR$13)/(12-(MONTH(TODAY())+ 1)),IF(MONTH(TODAY())=11,($BS$13-$BR$13)/2,IF(OR(MONTH(TODAY())=10,MONTH(TODAY())=12),($BS$13-$BR$13),0)))</f>
-        <v/>
-      </c>
-      <c r="BQ24" s="64" t="n"/>
-      <c r="BR24" s="66">
-        <f>SUM(IF(M24&lt;&gt;"",M24,IF(L24&lt;&gt;"",L24,K24)),IF(R24&lt;&gt;"",R24,IF(Q24&lt;&gt;"",Q24,P24)),IF(W24&lt;&gt;"",W24,IF(V24&lt;&gt;"",V24,U24)),IF(AB24&lt;&gt;"",AB24,IF(AA24&lt;&gt;"",AA24,Z24)),IF(AG24&lt;&gt;"",AG24,IF(AF24&lt;&gt;"",AF24,AE24)),IF(AL24&lt;&gt;"",AL24,IF(AK24&lt;&gt;"",AK24,AJ24)),IF(AQ24&lt;&gt;"",AQ24,IF(AP24&lt;&gt;"",AP24,AO24)),IF(AV24&lt;&gt;"",AV24,IF(AU24&lt;&gt;"",AU24,AT24)),IF(BA24&lt;&gt;"",BA24,IF(AZ24&lt;&gt;"",AZ24,AY24)),IF(BF24&lt;&gt;"",BF24,IF(BE24&lt;&gt;"",BE24,BD24)),IF(BK24&lt;&gt;"",BK24,IF(BJ24&lt;&gt;"",BJ24,BI24)),IF(BP24&lt;&gt;"",BP24,IF(BO24&lt;&gt;"",BO24,BN24)))</f>
-        <v/>
-      </c>
-      <c r="BS24" s="98" t="n"/>
-      <c r="BT24" s="99" t="n"/>
+      <c r="A24" s="88" t="n"/>
+      <c r="B24" s="89" t="n"/>
+      <c r="C24" s="90" t="n"/>
+      <c r="D24" s="90" t="n"/>
+      <c r="E24" s="89" t="n"/>
+      <c r="F24" s="89" t="n"/>
+      <c r="G24" s="89" t="n"/>
+      <c r="H24" s="89" t="n"/>
+      <c r="I24" s="91" t="n"/>
+      <c r="J24" s="92" t="n"/>
+      <c r="K24" s="93" t="n"/>
+      <c r="L24" s="93" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52">
+        <f>IF(OR(L23="",M23=""),"",L23-M23)</f>
+        <v/>
+      </c>
+      <c r="O24" s="92" t="n"/>
+      <c r="P24" s="93" t="n"/>
+      <c r="Q24" s="93" t="n"/>
+      <c r="R24" s="52" t="n"/>
+      <c r="S24" s="53">
+        <f>IF(OR(Q23="",R23=""),"",Q23-R23)</f>
+        <v/>
+      </c>
+      <c r="T24" s="58" t="n"/>
+      <c r="U24" s="93" t="n"/>
+      <c r="V24" s="93" t="n"/>
+      <c r="W24" s="52" t="n"/>
+      <c r="X24" s="53">
+        <f>IF(OR(V23="",W23=""),"",V23-W23)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="58" t="n"/>
+      <c r="Z24" s="93" t="n"/>
+      <c r="AA24" s="93" t="n"/>
+      <c r="AB24" s="52" t="n"/>
+      <c r="AC24" s="53">
+        <f>IF(OR(AA23="",AB23=""),"",AA23-AB23)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="58" t="n"/>
+      <c r="AE24" s="93" t="n"/>
+      <c r="AF24" s="93" t="n"/>
+      <c r="AG24" s="52" t="n"/>
+      <c r="AH24" s="53">
+        <f>IF(OR(AF23="",AG23=""),"",AF23-AG23)</f>
+        <v/>
+      </c>
+      <c r="AI24" s="58" t="n"/>
+      <c r="AJ24" s="93" t="n"/>
+      <c r="AK24" s="93" t="n"/>
+      <c r="AL24" s="52" t="n"/>
+      <c r="AM24" s="53">
+        <f>IF(OR(AK23="",AL23=""),"",AK23-AL23)</f>
+        <v/>
+      </c>
+      <c r="AN24" s="58" t="n"/>
+      <c r="AO24" s="93" t="n"/>
+      <c r="AP24" s="93" t="n"/>
+      <c r="AQ24" s="52" t="n"/>
+      <c r="AR24" s="53">
+        <f>IF(OR(AP23="",AQ23=""),"",AP23-AQ23)</f>
+        <v/>
+      </c>
+      <c r="AS24" s="58" t="n"/>
+      <c r="AT24" s="93" t="n"/>
+      <c r="AU24" s="93" t="n"/>
+      <c r="AV24" s="52" t="n"/>
+      <c r="AW24" s="53">
+        <f>IF(OR(AU23="",AV23=""),"",AU23-AV23)</f>
+        <v/>
+      </c>
+      <c r="AX24" s="58" t="n"/>
+      <c r="AY24" s="93" t="n"/>
+      <c r="AZ24" s="93" t="n"/>
+      <c r="BA24" s="52" t="n"/>
+      <c r="BB24" s="53">
+        <f>IF(OR(AZ23="",BA23=""),"",AZ23-BA23)</f>
+        <v/>
+      </c>
+      <c r="BC24" s="58" t="n"/>
+      <c r="BD24" s="93" t="n"/>
+      <c r="BE24" s="93" t="n"/>
+      <c r="BF24" s="52" t="n"/>
+      <c r="BG24" s="53">
+        <f>IF(OR(BE23="",BF23=""),"",BE23-BF23)</f>
+        <v/>
+      </c>
+      <c r="BH24" s="58" t="n"/>
+      <c r="BI24" s="93" t="n"/>
+      <c r="BJ24" s="93" t="n"/>
+      <c r="BK24" s="52" t="n"/>
+      <c r="BL24" s="53">
+        <f>IF(OR(BJ23="",BK23=""),"",BJ23-BK23)</f>
+        <v/>
+      </c>
+      <c r="BM24" s="58" t="n"/>
+      <c r="BN24" s="93" t="n"/>
+      <c r="BO24" s="93" t="n"/>
+      <c r="BP24" s="52" t="n"/>
+      <c r="BQ24" s="53">
+        <f>IF(OR(BO23="",BP23=""),"",BO23-BP23)</f>
+        <v/>
+      </c>
+      <c r="BR24" s="51">
+        <f>SUM(IF(M23&lt;&gt;"",M23,IF(L23&lt;&gt;"",L23,K23)),IF(R23&lt;&gt;"",R23,IF(Q23&lt;&gt;"",Q23,P23)),IF(W23&lt;&gt;"",W23,IF(V23&lt;&gt;"",V23,U23)),IF(AB23&lt;&gt;"",AB23,IF(AA23&lt;&gt;"",AA23,Z23)),IF(AG23&lt;&gt;"",AG23,IF(AF23&lt;&gt;"",AF23,AE23)),IF(AL23&lt;&gt;"",AL23,IF(AK23&lt;&gt;"",AK23,AJ23)),IF(AQ23&lt;&gt;"",AQ23,IF(AP23&lt;&gt;"",AP23,AO23)),IF(AV23&lt;&gt;"",AV23,IF(AU23&lt;&gt;"",AU23,AT23)),IF(BA23&lt;&gt;"",BA23,IF(AZ23&lt;&gt;"",AZ23,AY23)),IF(BF23&lt;&gt;"",BF23,IF(BE23&lt;&gt;"",BE23,BD23)),IF(BK23&lt;&gt;"",BK23,IF(BJ23&lt;&gt;"",BJ23,BI23)),IF(BP23&lt;&gt;"",BP23,IF(BO23&lt;&gt;"",BO23,BN23)))</f>
+        <v/>
+      </c>
+      <c r="BS24" s="94" t="n"/>
+      <c r="BT24" s="95" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="96" t="n"/>
+      <c r="D25" s="96" t="n"/>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="n"/>
+      <c r="G25" s="60" t="n"/>
+      <c r="H25" s="60" t="n"/>
+      <c r="I25" s="61" t="n"/>
+      <c r="J25" s="66" t="n"/>
+      <c r="K25" s="62" t="n"/>
+      <c r="L25" s="62" t="n"/>
+      <c r="M25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=1,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="97">
+        <f>IF(OR(L24="",M24=""),"",L24-M24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="66" t="n"/>
+      <c r="P25" s="62" t="n"/>
+      <c r="Q25" s="62" t="n"/>
+      <c r="R25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=2,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="S25" s="64" t="n"/>
+      <c r="T25" s="65" t="n"/>
+      <c r="U25" s="62" t="n"/>
+      <c r="V25" s="62" t="n"/>
+      <c r="W25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=3,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="X25" s="64" t="n"/>
+      <c r="Y25" s="65" t="n"/>
+      <c r="Z25" s="62" t="n"/>
+      <c r="AA25" s="62" t="n"/>
+      <c r="AB25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=4,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="64" t="n"/>
+      <c r="AD25" s="65" t="n"/>
+      <c r="AE25" s="62" t="n"/>
+      <c r="AF25" s="62" t="n"/>
+      <c r="AG25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=5,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="AH25" s="64" t="n"/>
+      <c r="AI25" s="65" t="n"/>
+      <c r="AJ25" s="62" t="n"/>
+      <c r="AK25" s="62" t="n"/>
+      <c r="AL25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=6,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="AM25" s="64" t="n"/>
+      <c r="AN25" s="65" t="n"/>
+      <c r="AO25" s="62" t="n"/>
+      <c r="AP25" s="62" t="n"/>
+      <c r="AQ25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=7,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="AR25" s="64" t="n"/>
+      <c r="AS25" s="65" t="n"/>
+      <c r="AT25" s="62" t="n"/>
+      <c r="AU25" s="62" t="n"/>
+      <c r="AV25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=8,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="AW25" s="64" t="n"/>
+      <c r="AX25" s="65" t="n"/>
+      <c r="AY25" s="62" t="n"/>
+      <c r="AZ25" s="62" t="n"/>
+      <c r="BA25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=9,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="BB25" s="64" t="n"/>
+      <c r="BC25" s="65" t="n"/>
+      <c r="BD25" s="62" t="n"/>
+      <c r="BE25" s="62" t="n"/>
+      <c r="BF25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=10,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),0)</f>
+        <v/>
+      </c>
+      <c r="BG25" s="64" t="n"/>
+      <c r="BH25" s="65" t="n"/>
+      <c r="BI25" s="62" t="n"/>
+      <c r="BJ25" s="62" t="n"/>
+      <c r="BK25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;=11,($BS$13-$BR$13)/(12-(MONTH(TODAY()) + 1)),IF(MONTH(TODAY())=11,($BS$13-$BR$13)/2,0))</f>
+        <v/>
+      </c>
+      <c r="BL25" s="64" t="n"/>
+      <c r="BM25" s="65" t="n"/>
+      <c r="BN25" s="62" t="n"/>
+      <c r="BO25" s="62" t="n"/>
+      <c r="BP25" s="63">
+        <f>IF((MONTH(TODAY()) + 2)&lt;12,($BS$13-$BR$13)/(12-(MONTH(TODAY())+ 1)),IF(MONTH(TODAY())=11,($BS$13-$BR$13)/2,IF(OR(MONTH(TODAY())=10,MONTH(TODAY())=12),($BS$13-$BR$13),0)))</f>
+        <v/>
+      </c>
+      <c r="BQ25" s="64" t="n"/>
+      <c r="BR25" s="66">
+        <f>SUM(IF(M24&lt;&gt;"",M24,IF(L24&lt;&gt;"",L24,K24)),IF(R24&lt;&gt;"",R24,IF(Q24&lt;&gt;"",Q24,P24)),IF(W24&lt;&gt;"",W24,IF(V24&lt;&gt;"",V24,U24)),IF(AB24&lt;&gt;"",AB24,IF(AA24&lt;&gt;"",AA24,Z24)),IF(AG24&lt;&gt;"",AG24,IF(AF24&lt;&gt;"",AF24,AE24)),IF(AL24&lt;&gt;"",AL24,IF(AK24&lt;&gt;"",AK24,AJ24)),IF(AQ24&lt;&gt;"",AQ24,IF(AP24&lt;&gt;"",AP24,AO24)),IF(AV24&lt;&gt;"",AV24,IF(AU24&lt;&gt;"",AU24,AT24)),IF(BA24&lt;&gt;"",BA24,IF(AZ24&lt;&gt;"",AZ24,AY24)),IF(BF24&lt;&gt;"",BF24,IF(BE24&lt;&gt;"",BE24,BD24)),IF(BK24&lt;&gt;"",BK24,IF(BJ24&lt;&gt;"",BJ24,BI24)),IF(BP24&lt;&gt;"",BP24,IF(BO24&lt;&gt;"",BO24,BN24)))</f>
+        <v/>
+      </c>
+      <c r="BS25" s="98" t="n"/>
+      <c r="BT25" s="99" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>EXPENSE END</t>
         </is>
       </c>
-      <c r="W25" s="19" t="n"/>
+      <c r="W26" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">

--- a/data/template_output.xlsx
+++ b/data/template_output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_62D044EBE908D790F21FCBFA54670B665EA485C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE125CF-4105-441A-A503-EDDF4ABF670E}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_62D044EBE908D790F21FCBFA54670B665EA485C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0726F3A-998B-446D-9695-160C775D2FF5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Transactions Source Data" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forecast Source Data'!$A$1:$AM$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Forecast Source Data'!$A$1:$AM$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Transactions Source Data'!$A$1:$AA$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1785,27 +1785,27 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1882,6 +1882,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2344,106 +2348,106 @@
         <f>SUM(J11:X11,Y12:BQ12)</f>
         <v>808971.62999999989</v>
       </c>
-      <c r="H11" s="136" t="s">
+      <c r="H11" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="137"/>
-      <c r="J11" s="131">
+      <c r="I11" s="132"/>
+      <c r="J11" s="136">
         <f t="array" ref="J11">SUM(M15:M25)+SUM(_xlfn._xlws.FILTER(L15:L25,M15:M25=""))+SUM(_xlfn._xlws.FILTER(K15:K25,(L15:L25="")*(M15:M25="")))+SUMIFS(N15:N25,M15:M25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(J15:J25)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="132"/>
-      <c r="L11" s="132"/>
-      <c r="M11" s="132"/>
-      <c r="N11" s="133"/>
-      <c r="O11" s="131">
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="135"/>
+      <c r="O11" s="136">
         <f t="array" ref="O11">SUM(R15:R25)+SUM(_xlfn._xlws.FILTER(Q15:Q25,R15:R25=""))+SUM(_xlfn._xlws.FILTER(P15:P25,(Q15:Q25="")*(R15:R25="")))+SUMIFS(S15:S25,R15:R25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(O15:O25)</f>
         <v>81595.28</v>
       </c>
-      <c r="P11" s="132"/>
-      <c r="Q11" s="132"/>
-      <c r="R11" s="132"/>
-      <c r="S11" s="133"/>
-      <c r="T11" s="131">
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="135"/>
+      <c r="T11" s="136">
         <f t="array" ref="T11">SUM(W15:W25)+SUM(_xlfn._xlws.FILTER(V15:V25,W15:W25=""))+SUM(_xlfn._xlws.FILTER(U15:U25,(V15:V25="")*(W15:W25="")))+SUMIFS(X15:X25,W15:W25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(T15:T25)</f>
         <v>154370.12999999998</v>
       </c>
-      <c r="U11" s="132"/>
-      <c r="V11" s="132"/>
-      <c r="W11" s="132"/>
-      <c r="X11" s="133"/>
-      <c r="Y11" s="131">
+      <c r="U11" s="134"/>
+      <c r="V11" s="134"/>
+      <c r="W11" s="134"/>
+      <c r="X11" s="135"/>
+      <c r="Y11" s="136">
         <f t="array" ref="Y11">SUM(AB15:AB25)+SUM(_xlfn._xlws.FILTER(AA15:AA25,AB15:AB25=""))+SUM(_xlfn._xlws.FILTER(Z15:Z25,(AA15:AA25="")*(AB15:AB25="")))+SUMIFS(AC15:AC25,AB15:AB25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(Y15:Y25)</f>
         <v>-154452.38</v>
       </c>
-      <c r="Z11" s="132"/>
-      <c r="AA11" s="132"/>
-      <c r="AB11" s="132"/>
-      <c r="AC11" s="133"/>
-      <c r="AD11" s="131">
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="135"/>
+      <c r="AD11" s="136">
         <f t="array" ref="AD11">SUM(AG15:AG25)+SUM(_xlfn._xlws.FILTER(AF15:AF25,AG15:AG25=""))+SUM(_xlfn._xlws.FILTER(AE15:AE25,(AF15:AF25="")*(AG15:AG25="")))+SUMIFS(AH15:AH25,AG15:AG25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AD15:AD25)</f>
         <v>-88040.880000000063</v>
       </c>
-      <c r="AE11" s="132"/>
-      <c r="AF11" s="132"/>
-      <c r="AG11" s="132"/>
-      <c r="AH11" s="133"/>
-      <c r="AI11" s="131">
+      <c r="AE11" s="134"/>
+      <c r="AF11" s="134"/>
+      <c r="AG11" s="134"/>
+      <c r="AH11" s="135"/>
+      <c r="AI11" s="136">
         <f t="array" ref="AI11">SUM(AL15:AL25)+SUM(_xlfn._xlws.FILTER(AK15:AK25,AL15:AL25=""))+SUM(_xlfn._xlws.FILTER(AJ15:AJ25,(AK15:AK25="")*(AL15:AL25="")))+SUMIFS(AM15:AM25,AL15:AL25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AI15:AI25)</f>
         <v>-12825.280000000028</v>
       </c>
-      <c r="AJ11" s="132"/>
-      <c r="AK11" s="132"/>
-      <c r="AL11" s="132"/>
-      <c r="AM11" s="133"/>
-      <c r="AN11" s="131">
+      <c r="AJ11" s="134"/>
+      <c r="AK11" s="134"/>
+      <c r="AL11" s="134"/>
+      <c r="AM11" s="135"/>
+      <c r="AN11" s="136">
         <f t="array" ref="AN11">SUM(AQ15:AQ25)+SUM(_xlfn._xlws.FILTER(AP15:AP25,AQ15:AQ25=""))+SUM(_xlfn._xlws.FILTER(AO15:AO25,(AP15:AP25="")*(AQ15:AQ25="")))+SUMIFS(AR15:AR25,AQ15:AQ25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AN15:AN25)</f>
         <v>10561.930000000022</v>
       </c>
-      <c r="AO11" s="132"/>
-      <c r="AP11" s="132"/>
-      <c r="AQ11" s="132"/>
-      <c r="AR11" s="133"/>
-      <c r="AS11" s="131">
+      <c r="AO11" s="134"/>
+      <c r="AP11" s="134"/>
+      <c r="AQ11" s="134"/>
+      <c r="AR11" s="135"/>
+      <c r="AS11" s="136">
         <f t="array" ref="AS11">SUM(AV15:AV25)+SUM(_xlfn._xlws.FILTER(AU15:AU25,AV15:AV25=""))+SUM(_xlfn._xlws.FILTER(AT15:AT25,(AU15:AU25="")*(AV15:AV25="")))+SUMIFS(AW15:AW25,AV15:AV25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AS15:AS25)</f>
         <v>-133523.93</v>
       </c>
-      <c r="AT11" s="132"/>
-      <c r="AU11" s="132"/>
-      <c r="AV11" s="132"/>
-      <c r="AW11" s="133"/>
-      <c r="AX11" s="131">
+      <c r="AT11" s="134"/>
+      <c r="AU11" s="134"/>
+      <c r="AV11" s="134"/>
+      <c r="AW11" s="135"/>
+      <c r="AX11" s="136">
         <f t="array" ref="AX11">SUM(BA15:BA25)+SUM(_xlfn._xlws.FILTER(AZ15:AZ25,BA15:BA25=""))+SUM(_xlfn._xlws.FILTER(AY15:AY25,(AZ15:AZ25="")*(BA15:BA25="")))+SUMIFS(BB15:BB25,BA15:BA25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AX15:AX25)</f>
         <v>10624</v>
       </c>
-      <c r="AY11" s="132"/>
-      <c r="AZ11" s="132"/>
-      <c r="BA11" s="132"/>
-      <c r="BB11" s="133"/>
-      <c r="BC11" s="131">
+      <c r="AY11" s="134"/>
+      <c r="AZ11" s="134"/>
+      <c r="BA11" s="134"/>
+      <c r="BB11" s="135"/>
+      <c r="BC11" s="136">
         <f t="array" ref="BC11">SUM(BF15:BF25)+SUM(_xlfn._xlws.FILTER(BE15:BE25,BF15:BF25=""))+SUM(_xlfn._xlws.FILTER(BD15:BD25,(BE15:BE25="")*(BF15:BF25="")))+SUMIFS(BG15:BG25,BF15:BF25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BC15:BC25)</f>
         <v>0</v>
       </c>
-      <c r="BD11" s="132"/>
-      <c r="BE11" s="132"/>
-      <c r="BF11" s="132"/>
-      <c r="BG11" s="133"/>
-      <c r="BH11" s="131">
+      <c r="BD11" s="134"/>
+      <c r="BE11" s="134"/>
+      <c r="BF11" s="134"/>
+      <c r="BG11" s="135"/>
+      <c r="BH11" s="136">
         <f t="array" ref="BH11">SUM(BK15:BK25)+SUM(_xlfn._xlws.FILTER(BJ15:BJ25,BK15:BK25=""))+SUM(_xlfn._xlws.FILTER(BI15:BI25,(BJ15:BJ25="")*(BK15:BK25="")))+SUMIFS(BL15:BL25,BK15:BK25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BH15:BH25)</f>
         <v>0</v>
       </c>
-      <c r="BI11" s="132"/>
-      <c r="BJ11" s="132"/>
-      <c r="BK11" s="132"/>
-      <c r="BL11" s="133"/>
-      <c r="BM11" s="131">
+      <c r="BI11" s="134"/>
+      <c r="BJ11" s="134"/>
+      <c r="BK11" s="134"/>
+      <c r="BL11" s="135"/>
+      <c r="BM11" s="136">
         <f t="array" ref="BM11">SUM(BP15:BP25)+SUM(_xlfn._xlws.FILTER(BO15:BO25,BP15:BP25=""))+SUM(_xlfn._xlws.FILTER(BN15:BN25,(BO15:BO25="")*(BP15:BP25="")))+SUMIFS(BQ15:BQ25,BP15:BP25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BM15:BM25)</f>
         <v>0</v>
       </c>
-      <c r="BN11" s="132"/>
-      <c r="BO11" s="132"/>
-      <c r="BP11" s="132"/>
-      <c r="BQ11" s="133"/>
+      <c r="BN11" s="134"/>
+      <c r="BO11" s="134"/>
+      <c r="BP11" s="134"/>
+      <c r="BQ11" s="135"/>
       <c r="BR11" s="21" t="s">
         <v>17</v>
       </c>
@@ -2475,106 +2479,106 @@
         <f>G11-G10</f>
         <v>808971.62999999989</v>
       </c>
-      <c r="H12" s="140" t="s">
+      <c r="H12" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="137"/>
-      <c r="J12" s="131">
+      <c r="I12" s="132"/>
+      <c r="J12" s="136">
         <f t="array" ref="J12">SUM(M15:M25)+SUM(_xlfn._xlws.FILTER(L15:L25,M15:M25=""))+SUM(_xlfn._xlws.FILTER(K15:K25,(L15:L25="")*(M15:M25="")))</f>
         <v>47862.5</v>
       </c>
-      <c r="K12" s="132"/>
-      <c r="L12" s="132"/>
-      <c r="M12" s="132"/>
-      <c r="N12" s="133"/>
-      <c r="O12" s="131">
+      <c r="K12" s="134"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="134"/>
+      <c r="N12" s="135"/>
+      <c r="O12" s="136">
         <f t="array" ref="O12">SUM(R15:R25)+SUM(_xlfn._xlws.FILTER(Q15:Q25,R15:R25=""))+SUM(_xlfn._xlws.FILTER(P15:P25,(Q15:Q25="")*(R15:R25="")))</f>
         <v>17100</v>
       </c>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="132"/>
-      <c r="R12" s="132"/>
-      <c r="S12" s="133"/>
-      <c r="T12" s="131">
+      <c r="P12" s="134"/>
+      <c r="Q12" s="134"/>
+      <c r="R12" s="134"/>
+      <c r="S12" s="135"/>
+      <c r="T12" s="136">
         <f t="array" ref="T12">SUM(W15:W25)+SUM(_xlfn._xlws.FILTER(V15:V25,W15:W25=""))+SUM(_xlfn._xlws.FILTER(U15:U25,(V15:V25="")*(W15:W25="")))</f>
         <v>162177</v>
       </c>
-      <c r="U12" s="132"/>
-      <c r="V12" s="132"/>
-      <c r="W12" s="132"/>
-      <c r="X12" s="133"/>
-      <c r="Y12" s="131">
+      <c r="U12" s="134"/>
+      <c r="V12" s="134"/>
+      <c r="W12" s="134"/>
+      <c r="X12" s="135"/>
+      <c r="Y12" s="136">
         <f t="array" ref="Y12">SUM(AB15:AB25)+SUM(_xlfn._xlws.FILTER(AA15:AA25,AB15:AB25=""))+SUM(_xlfn._xlws.FILTER(Z15:Z25,(AA15:AA25="")*(AB15:AB25="")))</f>
         <v>174087.5</v>
       </c>
-      <c r="Z12" s="132"/>
-      <c r="AA12" s="132"/>
-      <c r="AB12" s="132"/>
-      <c r="AC12" s="133"/>
-      <c r="AD12" s="131">
+      <c r="Z12" s="134"/>
+      <c r="AA12" s="134"/>
+      <c r="AB12" s="134"/>
+      <c r="AC12" s="135"/>
+      <c r="AD12" s="136">
         <f t="array" ref="AD12">SUM(AG15:AG25)+SUM(_xlfn._xlws.FILTER(AF15:AF25,AG15:AG25=""))+SUM(_xlfn._xlws.FILTER(AE15:AE25,(AF15:AF25="")*(AG15:AG25="")))</f>
         <v>164242.5</v>
       </c>
-      <c r="AE12" s="132"/>
-      <c r="AF12" s="132"/>
-      <c r="AG12" s="132"/>
-      <c r="AH12" s="133"/>
-      <c r="AI12" s="131">
+      <c r="AE12" s="134"/>
+      <c r="AF12" s="134"/>
+      <c r="AG12" s="134"/>
+      <c r="AH12" s="135"/>
+      <c r="AI12" s="136">
         <f t="array" ref="AI12">SUM(AL15:AL25)+SUM(_xlfn._xlws.FILTER(AK15:AK25,AL15:AL25=""))+SUM(_xlfn._xlws.FILTER(AJ15:AJ25,(AK15:AK25="")*(AL15:AL25="")))</f>
         <v>138958.5</v>
       </c>
-      <c r="AJ12" s="132"/>
-      <c r="AK12" s="132"/>
-      <c r="AL12" s="132"/>
-      <c r="AM12" s="133"/>
-      <c r="AN12" s="131">
+      <c r="AJ12" s="134"/>
+      <c r="AK12" s="134"/>
+      <c r="AL12" s="134"/>
+      <c r="AM12" s="135"/>
+      <c r="AN12" s="136">
         <f t="array" ref="AN12">SUM(AQ15:AQ25)+SUM(_xlfn._xlws.FILTER(AP15:AP25,AQ15:AQ25=""))+SUM(_xlfn._xlws.FILTER(AO15:AO25,(AP15:AP25="")*(AQ15:AQ25="")))</f>
         <v>40810.199999999997</v>
       </c>
-      <c r="AO12" s="132"/>
-      <c r="AP12" s="132"/>
-      <c r="AQ12" s="132"/>
-      <c r="AR12" s="133"/>
-      <c r="AS12" s="131">
+      <c r="AO12" s="134"/>
+      <c r="AP12" s="134"/>
+      <c r="AQ12" s="134"/>
+      <c r="AR12" s="135"/>
+      <c r="AS12" s="136">
         <f t="array" ref="AS12">SUM(AV15:AV25)+SUM(_xlfn._xlws.FILTER(AU15:AU25,AV15:AV25=""))+SUM(_xlfn._xlws.FILTER(AT15:AT25,(AU15:AU25="")*(AV15:AV25="")))</f>
         <v>54907.519999999997</v>
       </c>
-      <c r="AT12" s="132"/>
-      <c r="AU12" s="132"/>
-      <c r="AV12" s="132"/>
-      <c r="AW12" s="133"/>
-      <c r="AX12" s="131">
+      <c r="AT12" s="134"/>
+      <c r="AU12" s="134"/>
+      <c r="AV12" s="134"/>
+      <c r="AW12" s="135"/>
+      <c r="AX12" s="136">
         <f t="array" ref="AX12">SUM(BA15:BA25)+SUM(_xlfn._xlws.FILTER(AZ15:AZ25,BA15:BA25=""))+SUM(_xlfn._xlws.FILTER(AY15:AY25,(AZ15:AZ25="")*(BA15:BA25="")))</f>
         <v>0</v>
       </c>
-      <c r="AY12" s="132"/>
-      <c r="AZ12" s="132"/>
-      <c r="BA12" s="132"/>
-      <c r="BB12" s="133"/>
-      <c r="BC12" s="131">
+      <c r="AY12" s="134"/>
+      <c r="AZ12" s="134"/>
+      <c r="BA12" s="134"/>
+      <c r="BB12" s="135"/>
+      <c r="BC12" s="136">
         <f t="array" ref="BC12">SUM(BF15:BF25)+SUM(_xlfn._xlws.FILTER(BE15:BE25,BF15:BF25=""))+SUM(_xlfn._xlws.FILTER(BD15:BD25,(BE15:BE25="")*(BF15:BF25="")))</f>
         <v>0</v>
       </c>
-      <c r="BD12" s="132"/>
-      <c r="BE12" s="132"/>
-      <c r="BF12" s="132"/>
-      <c r="BG12" s="133"/>
-      <c r="BH12" s="131">
+      <c r="BD12" s="134"/>
+      <c r="BE12" s="134"/>
+      <c r="BF12" s="134"/>
+      <c r="BG12" s="135"/>
+      <c r="BH12" s="136">
         <f t="array" ref="BH12">SUM(BK15:BK25)+SUM(_xlfn._xlws.FILTER(BJ15:BJ25,BK15:BK25=""))+SUM(_xlfn._xlws.FILTER(BI15:BI25,(BJ15:BJ25="")*(BK15:BK25="")))</f>
         <v>0</v>
       </c>
-      <c r="BI12" s="132"/>
-      <c r="BJ12" s="132"/>
-      <c r="BK12" s="132"/>
-      <c r="BL12" s="133"/>
-      <c r="BM12" s="131">
+      <c r="BI12" s="134"/>
+      <c r="BJ12" s="134"/>
+      <c r="BK12" s="134"/>
+      <c r="BL12" s="135"/>
+      <c r="BM12" s="136">
         <f t="array" ref="BM12">SUM(BP15:BP25)+SUM(_xlfn._xlws.FILTER(BO15:BO25,BP15:BP25=""))+SUM(_xlfn._xlws.FILTER(BN15:BN25,(BO15:BO25="")*(BP15:BP25="")))</f>
         <v>0</v>
       </c>
-      <c r="BN12" s="132"/>
-      <c r="BO12" s="132"/>
-      <c r="BP12" s="132"/>
-      <c r="BQ12" s="133"/>
+      <c r="BN12" s="134"/>
+      <c r="BO12" s="134"/>
+      <c r="BP12" s="134"/>
+      <c r="BQ12" s="135"/>
       <c r="BR12" s="21"/>
       <c r="BS12" s="22"/>
     </row>
@@ -2586,90 +2590,90 @@
         <v>22</v>
       </c>
       <c r="I13" s="139"/>
-      <c r="J13" s="135">
+      <c r="J13" s="140">
         <v>45322</v>
       </c>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="134">
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="133">
         <v>45351</v>
       </c>
-      <c r="P13" s="132"/>
-      <c r="Q13" s="132"/>
-      <c r="R13" s="132"/>
-      <c r="S13" s="133"/>
-      <c r="T13" s="134">
+      <c r="P13" s="134"/>
+      <c r="Q13" s="134"/>
+      <c r="R13" s="134"/>
+      <c r="S13" s="135"/>
+      <c r="T13" s="133">
         <v>45382</v>
       </c>
-      <c r="U13" s="132"/>
-      <c r="V13" s="132"/>
-      <c r="W13" s="132"/>
-      <c r="X13" s="133"/>
-      <c r="Y13" s="134">
+      <c r="U13" s="134"/>
+      <c r="V13" s="134"/>
+      <c r="W13" s="134"/>
+      <c r="X13" s="135"/>
+      <c r="Y13" s="133">
         <v>45412</v>
       </c>
-      <c r="Z13" s="132"/>
-      <c r="AA13" s="132"/>
-      <c r="AB13" s="132"/>
-      <c r="AC13" s="133"/>
-      <c r="AD13" s="134">
+      <c r="Z13" s="134"/>
+      <c r="AA13" s="134"/>
+      <c r="AB13" s="134"/>
+      <c r="AC13" s="135"/>
+      <c r="AD13" s="133">
         <v>45443</v>
       </c>
-      <c r="AE13" s="132"/>
-      <c r="AF13" s="132"/>
-      <c r="AG13" s="132"/>
-      <c r="AH13" s="133"/>
-      <c r="AI13" s="134">
+      <c r="AE13" s="134"/>
+      <c r="AF13" s="134"/>
+      <c r="AG13" s="134"/>
+      <c r="AH13" s="135"/>
+      <c r="AI13" s="133">
         <v>45473</v>
       </c>
-      <c r="AJ13" s="132"/>
-      <c r="AK13" s="132"/>
-      <c r="AL13" s="132"/>
-      <c r="AM13" s="133"/>
-      <c r="AN13" s="134">
+      <c r="AJ13" s="134"/>
+      <c r="AK13" s="134"/>
+      <c r="AL13" s="134"/>
+      <c r="AM13" s="135"/>
+      <c r="AN13" s="133">
         <v>45504</v>
       </c>
-      <c r="AO13" s="132"/>
-      <c r="AP13" s="132"/>
-      <c r="AQ13" s="132"/>
-      <c r="AR13" s="133"/>
-      <c r="AS13" s="134">
+      <c r="AO13" s="134"/>
+      <c r="AP13" s="134"/>
+      <c r="AQ13" s="134"/>
+      <c r="AR13" s="135"/>
+      <c r="AS13" s="133">
         <v>45535</v>
       </c>
-      <c r="AT13" s="132"/>
-      <c r="AU13" s="132"/>
-      <c r="AV13" s="132"/>
-      <c r="AW13" s="133"/>
-      <c r="AX13" s="134">
+      <c r="AT13" s="134"/>
+      <c r="AU13" s="134"/>
+      <c r="AV13" s="134"/>
+      <c r="AW13" s="135"/>
+      <c r="AX13" s="133">
         <v>45565</v>
       </c>
-      <c r="AY13" s="132"/>
-      <c r="AZ13" s="132"/>
-      <c r="BA13" s="132"/>
-      <c r="BB13" s="133"/>
-      <c r="BC13" s="134">
+      <c r="AY13" s="134"/>
+      <c r="AZ13" s="134"/>
+      <c r="BA13" s="134"/>
+      <c r="BB13" s="135"/>
+      <c r="BC13" s="133">
         <v>45596</v>
       </c>
-      <c r="BD13" s="132"/>
-      <c r="BE13" s="132"/>
-      <c r="BF13" s="132"/>
-      <c r="BG13" s="133"/>
-      <c r="BH13" s="134">
+      <c r="BD13" s="134"/>
+      <c r="BE13" s="134"/>
+      <c r="BF13" s="134"/>
+      <c r="BG13" s="135"/>
+      <c r="BH13" s="133">
         <v>45626</v>
       </c>
-      <c r="BI13" s="132"/>
-      <c r="BJ13" s="132"/>
-      <c r="BK13" s="132"/>
-      <c r="BL13" s="133"/>
-      <c r="BM13" s="134">
+      <c r="BI13" s="134"/>
+      <c r="BJ13" s="134"/>
+      <c r="BK13" s="134"/>
+      <c r="BL13" s="135"/>
+      <c r="BM13" s="133">
         <v>45657</v>
       </c>
-      <c r="BN13" s="132"/>
-      <c r="BO13" s="132"/>
-      <c r="BP13" s="132"/>
-      <c r="BQ13" s="133"/>
+      <c r="BN13" s="134"/>
+      <c r="BO13" s="134"/>
+      <c r="BP13" s="134"/>
+      <c r="BQ13" s="135"/>
       <c r="BR13" s="24">
         <f>SUM(BR15:BR24)</f>
         <v>800145.72</v>
@@ -4769,13 +4773,20 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="AS13:AW13"/>
-    <mergeCell ref="BC13:BG13"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AI12:AM12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="AN13:AR13"/>
+    <mergeCell ref="BM12:BQ12"/>
+    <mergeCell ref="BC11:BG11"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="BM11:BQ11"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="BH12:BL12"/>
+    <mergeCell ref="AX11:BB11"/>
+    <mergeCell ref="AS12:AW12"/>
+    <mergeCell ref="AI11:AM11"/>
+    <mergeCell ref="BM13:BQ13"/>
+    <mergeCell ref="BH13:BL13"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="BH11:BL11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="T12:X12"/>
     <mergeCell ref="J11:N11"/>
@@ -4792,22 +4803,15 @@
     <mergeCell ref="O13:S13"/>
     <mergeCell ref="T13:X13"/>
     <mergeCell ref="O12:S12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="AS13:AW13"/>
+    <mergeCell ref="BC13:BG13"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AI12:AM12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="AN13:AR13"/>
     <mergeCell ref="AD12:AH12"/>
     <mergeCell ref="AI13:AM13"/>
-    <mergeCell ref="BM12:BQ12"/>
-    <mergeCell ref="BC11:BG11"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="BM11:BQ11"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="BH12:BL12"/>
-    <mergeCell ref="AX11:BB11"/>
-    <mergeCell ref="AS12:AW12"/>
-    <mergeCell ref="AI11:AM11"/>
-    <mergeCell ref="BM13:BQ13"/>
-    <mergeCell ref="BH13:BL13"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="BH11:BL11"/>
   </mergeCells>
   <conditionalFormatting sqref="M15:M24 R15:R24 W15:W24 AB15:AB24 AG15:AG24 AL15:AL24 AQ15:AQ24 AV15:AV24 BA15:BA24 BF15:BF24 BK15:BK24 BP15:BP24">
     <cfRule type="expression" dxfId="7" priority="8">
@@ -4856,11 +4860,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AM12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="25" width="13" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="9.140625" collapsed="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="11.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="17.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="13" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="49.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="18.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="18" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="19.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="25.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="10.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="17.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="10.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="22.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="16" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="21.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="17.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="21" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="19.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="15.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="24.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="18.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="19" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="12.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="12.85546875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -4982,7 +5023,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -5083,7 +5124,7 @@
         <v>292710</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -5386,7 +5427,7 @@
         <v>53865</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -5487,7 +5528,7 @@
         <v>131000</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -5588,7 +5629,7 @@
         <v>169000</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -5689,7 +5730,7 @@
         <v>54292.5</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -5790,7 +5831,7 @@
         <v>254000</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -5891,7 +5932,7 @@
         <v>154432</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -5998,7 +6039,7 @@
       </c>
       <c r="O12">
         <f>SUBTOTAL(9, O2:O11)</f>
-        <v>211526.5</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <f>SUBTOTAL(9, P2:P11)</f>
@@ -6006,67 +6047,73 @@
       </c>
       <c r="Q12">
         <f>SUBTOTAL(9, Q2:Q11)</f>
-        <v>211526.5</v>
+        <v>0</v>
       </c>
       <c r="Z12">
         <f t="shared" ref="Z12:AM12" si="0">SUBTOTAL(9, Z2:Z11)</f>
-        <v>6019</v>
+        <v>18</v>
       </c>
       <c r="AA12">
         <f t="shared" si="0"/>
-        <v>69575</v>
+        <v>14535</v>
       </c>
       <c r="AB12">
         <f t="shared" si="0"/>
-        <v>92690</v>
+        <v>17100</v>
       </c>
       <c r="AC12">
         <f t="shared" si="0"/>
-        <v>135175</v>
+        <v>21375</v>
       </c>
       <c r="AD12">
         <f t="shared" si="0"/>
-        <v>110590</v>
+        <v>15390</v>
       </c>
       <c r="AE12">
         <f t="shared" si="0"/>
-        <v>112300</v>
+        <v>17100</v>
       </c>
       <c r="AF12">
         <f t="shared" si="0"/>
-        <v>133255</v>
+        <v>21375</v>
       </c>
       <c r="AG12">
         <f t="shared" si="0"/>
-        <v>154278</v>
+        <v>855</v>
       </c>
       <c r="AH12">
         <f t="shared" si="0"/>
-        <v>160670</v>
+        <v>0</v>
       </c>
       <c r="AI12">
         <f t="shared" si="0"/>
-        <v>198827.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
         <f t="shared" si="0"/>
-        <v>159387.5</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f t="shared" si="0"/>
-        <v>158310</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <f t="shared" si="0"/>
-        <v>211526.5</v>
+        <v>0</v>
       </c>
       <c r="AM12">
         <f t="shared" si="0"/>
-        <v>1696584.5</v>
+        <v>107730</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM12" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AM11" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="9500879389"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6177,7 +6224,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -6260,7 +6307,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -6343,7 +6390,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -6426,7 +6473,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -6509,7 +6556,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -6675,7 +6722,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -6758,7 +6805,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -6841,7 +6888,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -8169,7 +8216,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>83</v>
       </c>
@@ -8252,7 +8299,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -8335,7 +8382,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -8418,7 +8465,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -8501,7 +8548,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -8584,7 +8631,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -8667,7 +8714,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -8750,7 +8797,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -8833,7 +8880,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -8916,7 +8963,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -8999,7 +9046,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -10493,7 +10540,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="54" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>84</v>
       </c>
@@ -12070,7 +12117,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="73" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -12153,7 +12200,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="74" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -12236,7 +12283,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="75" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -14809,7 +14856,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="106" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>84</v>
       </c>
@@ -14894,10 +14941,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AA106" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="202502"/>
-        <filter val="202503"/>
+        <filter val="9500887310"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Accrual"/>
+        <filter val="Reversal"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/template_output.xlsx
+++ b/data/template_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pfizer-my.sharepoint.com/personal/hoveyo_pfizer_com/Documents/financial-automation-project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_53563E9B681595B0F7239972BC8032DCB2E48D80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B51FD2-2639-49C3-B5C1-4AC7A0CF7C19}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_53563E9B681595B0F7239972BC8032DCB2E48D80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225097DF-B6D0-4122-AE89-AA7BA7CAC9B3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23220" windowHeight="12390" tabRatio="590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -1793,27 +1793,27 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2352,106 +2352,106 @@
         <f ca="1">SUM(J11:X11,Y12:BQ12)</f>
         <v>-15621.779999999962</v>
       </c>
-      <c r="H11" s="143" t="s">
+      <c r="H11" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="144"/>
-      <c r="J11" s="138">
+      <c r="I11" s="139"/>
+      <c r="J11" s="143">
         <f t="array" aca="1" ref="J11" ca="1">SUM(M15:M25)+SUM(_xlfn._xlws.FILTER(L15:L25,M15:M25=""))+SUM(_xlfn._xlws.FILTER(K15:K25,(L15:L25="")*(M15:M25="")))+SUMIFS(N15:N25,M15:M25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(J15:J25)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="139"/>
-      <c r="L11" s="139"/>
-      <c r="M11" s="139"/>
-      <c r="N11" s="140"/>
-      <c r="O11" s="138">
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="143">
         <f t="array" aca="1" ref="O11" ca="1">SUM(R15:R25)+SUM(_xlfn._xlws.FILTER(Q15:Q25,R15:R25=""))+SUM(_xlfn._xlws.FILTER(P15:P25,(Q15:Q25="")*(R15:R25="")))+SUMIFS(S15:S25,R15:R25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(O15:O25)</f>
         <v>81595.28</v>
       </c>
-      <c r="P11" s="139"/>
-      <c r="Q11" s="139"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="140"/>
-      <c r="T11" s="138">
+      <c r="P11" s="141"/>
+      <c r="Q11" s="141"/>
+      <c r="R11" s="141"/>
+      <c r="S11" s="142"/>
+      <c r="T11" s="143">
         <f t="array" aca="1" ref="T11" ca="1">SUM(W15:W25)+SUM(_xlfn._xlws.FILTER(V15:V25,W15:W25=""))+SUM(_xlfn._xlws.FILTER(U15:U25,(V15:V25="")*(W15:W25="")))+SUMIFS(X15:X25,W15:W25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(T15:T25)</f>
         <v>46818.44</v>
       </c>
-      <c r="U11" s="139"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="139"/>
-      <c r="X11" s="140"/>
-      <c r="Y11" s="138">
+      <c r="U11" s="141"/>
+      <c r="V11" s="141"/>
+      <c r="W11" s="141"/>
+      <c r="X11" s="142"/>
+      <c r="Y11" s="143">
         <f t="array" aca="1" ref="Y11" ca="1">SUM(AB15:AB25)+SUM(_xlfn._xlws.FILTER(AA15:AA25,AB15:AB25=""))+SUM(_xlfn._xlws.FILTER(Z15:Z25,(AA15:AA25="")*(AB15:AB25="")))+SUMIFS(AC15:AC25,AB15:AB25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(Y15:Y25)</f>
         <v>-54655.164444444439</v>
       </c>
-      <c r="Z11" s="139"/>
-      <c r="AA11" s="139"/>
-      <c r="AB11" s="139"/>
-      <c r="AC11" s="140"/>
-      <c r="AD11" s="138">
+      <c r="Z11" s="141"/>
+      <c r="AA11" s="141"/>
+      <c r="AB11" s="141"/>
+      <c r="AC11" s="142"/>
+      <c r="AD11" s="143">
         <f t="array" aca="1" ref="AD11" ca="1">SUM(AG15:AG25)+SUM(_xlfn._xlws.FILTER(AF15:AF25,AG15:AG25=""))+SUM(_xlfn._xlws.FILTER(AE15:AE25,(AF15:AF25="")*(AG15:AG25="")))+SUMIFS(AH15:AH25,AG15:AG25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AD15:AD25)</f>
         <v>-9477.6644444444391</v>
       </c>
-      <c r="AE11" s="139"/>
-      <c r="AF11" s="139"/>
-      <c r="AG11" s="139"/>
-      <c r="AH11" s="140"/>
-      <c r="AI11" s="138">
+      <c r="AE11" s="141"/>
+      <c r="AF11" s="141"/>
+      <c r="AG11" s="141"/>
+      <c r="AH11" s="142"/>
+      <c r="AI11" s="143">
         <f t="array" aca="1" ref="AI11" ca="1">SUM(AL15:AL25)+SUM(_xlfn._xlws.FILTER(AK15:AK25,AL15:AL25=""))+SUM(_xlfn._xlws.FILTER(AJ15:AJ25,(AK15:AK25="")*(AL15:AL25="")))+SUMIFS(AM15:AM25,AL15:AL25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AI15:AI25)</f>
         <v>-52174.224444444437</v>
       </c>
-      <c r="AJ11" s="139"/>
-      <c r="AK11" s="139"/>
-      <c r="AL11" s="139"/>
-      <c r="AM11" s="140"/>
-      <c r="AN11" s="138">
+      <c r="AJ11" s="141"/>
+      <c r="AK11" s="141"/>
+      <c r="AL11" s="141"/>
+      <c r="AM11" s="142"/>
+      <c r="AN11" s="143">
         <f t="array" aca="1" ref="AN11" ca="1">SUM(AQ15:AQ25)+SUM(_xlfn._xlws.FILTER(AP15:AP25,AQ15:AQ25=""))+SUM(_xlfn._xlws.FILTER(AO15:AO25,(AP15:AP25="")*(AQ15:AQ25="")))+SUMIFS(AR15:AR25,AQ15:AQ25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AN15:AN25)</f>
         <v>-94366.444444444438</v>
       </c>
-      <c r="AO11" s="139"/>
-      <c r="AP11" s="139"/>
-      <c r="AQ11" s="139"/>
-      <c r="AR11" s="140"/>
-      <c r="AS11" s="138">
+      <c r="AO11" s="141"/>
+      <c r="AP11" s="141"/>
+      <c r="AQ11" s="141"/>
+      <c r="AR11" s="142"/>
+      <c r="AS11" s="143">
         <f t="array" aca="1" ref="AS11" ca="1">SUM(AV15:AV25)+SUM(_xlfn._xlws.FILTER(AU15:AU25,AV15:AV25=""))+SUM(_xlfn._xlws.FILTER(AT15:AT25,(AU15:AU25="")*(AV15:AV25="")))+SUMIFS(AW15:AW25,AV15:AV25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AS15:AS25)</f>
         <v>-99787.444444444438</v>
       </c>
-      <c r="AT11" s="139"/>
-      <c r="AU11" s="139"/>
-      <c r="AV11" s="139"/>
-      <c r="AW11" s="140"/>
-      <c r="AX11" s="138">
+      <c r="AT11" s="141"/>
+      <c r="AU11" s="141"/>
+      <c r="AV11" s="141"/>
+      <c r="AW11" s="142"/>
+      <c r="AX11" s="143">
         <f t="array" aca="1" ref="AX11" ca="1">SUM(BA15:BA25)+SUM(_xlfn._xlws.FILTER(AZ15:AZ25,BA15:BA25=""))+SUM(_xlfn._xlws.FILTER(AY15:AY25,(AZ15:AZ25="")*(BA15:BA25="")))+SUMIFS(BB15:BB25,BA15:BA25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(AX15:AX25)</f>
         <v>18688.055555555555</v>
       </c>
-      <c r="AY11" s="139"/>
-      <c r="AZ11" s="139"/>
-      <c r="BA11" s="139"/>
-      <c r="BB11" s="140"/>
-      <c r="BC11" s="138">
+      <c r="AY11" s="141"/>
+      <c r="AZ11" s="141"/>
+      <c r="BA11" s="141"/>
+      <c r="BB11" s="142"/>
+      <c r="BC11" s="143">
         <f t="array" aca="1" ref="BC11" ca="1">SUM(BF15:BF25)+SUM(_xlfn._xlws.FILTER(BE15:BE25,BF15:BF25=""))+SUM(_xlfn._xlws.FILTER(BD15:BD25,(BE15:BE25="")*(BF15:BF25="")))+SUMIFS(BG15:BG25,BF15:BF25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BC15:BC25)</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BD11" s="139"/>
-      <c r="BE11" s="139"/>
-      <c r="BF11" s="139"/>
-      <c r="BG11" s="140"/>
-      <c r="BH11" s="138">
+      <c r="BD11" s="141"/>
+      <c r="BE11" s="141"/>
+      <c r="BF11" s="141"/>
+      <c r="BG11" s="142"/>
+      <c r="BH11" s="143">
         <f t="array" aca="1" ref="BH11" ca="1">SUM(BK15:BK25)+SUM(_xlfn._xlws.FILTER(BJ15:BJ25,BK15:BK25=""))+SUM(_xlfn._xlws.FILTER(BI15:BI25,(BJ15:BJ25="")*(BK15:BK25="")))+SUMIFS(BL15:BL25,BK15:BK25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BH15:BH25)</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BI11" s="139"/>
-      <c r="BJ11" s="139"/>
-      <c r="BK11" s="139"/>
-      <c r="BL11" s="140"/>
-      <c r="BM11" s="138">
+      <c r="BI11" s="141"/>
+      <c r="BJ11" s="141"/>
+      <c r="BK11" s="141"/>
+      <c r="BL11" s="142"/>
+      <c r="BM11" s="143">
         <f t="array" aca="1" ref="BM11" ca="1">SUM(BP15:BP25)+SUM(_xlfn._xlws.FILTER(BO15:BO25,BP15:BP25=""))+SUM(_xlfn._xlws.FILTER(BN15:BN25,(BO15:BO25="")*(BP15:BP25="")))+SUMIFS(BQ15:BQ25,BP15:BP25,"&lt;&gt;"&amp;"",$L$15:$L$25,"&lt;&gt;"&amp;"")+SUM(BM15:BM25)</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BN11" s="139"/>
-      <c r="BO11" s="139"/>
-      <c r="BP11" s="139"/>
-      <c r="BQ11" s="140"/>
+      <c r="BN11" s="141"/>
+      <c r="BO11" s="141"/>
+      <c r="BP11" s="141"/>
+      <c r="BQ11" s="142"/>
       <c r="BR11" s="21" t="s">
         <v>17</v>
       </c>
@@ -2483,106 +2483,106 @@
         <f ca="1">G11-G10</f>
         <v>-15621.779999999962</v>
       </c>
-      <c r="H12" s="147" t="s">
+      <c r="H12" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="144"/>
-      <c r="J12" s="138">
+      <c r="I12" s="139"/>
+      <c r="J12" s="143">
         <f t="array" aca="1" ref="J12" ca="1">SUM(M15:M25)+SUM(_xlfn._xlws.FILTER(L15:L25,M15:M25=""))+SUM(_xlfn._xlws.FILTER(K15:K25,(L15:L25="")*(M15:M25="")))</f>
         <v>47862.5</v>
       </c>
-      <c r="K12" s="139"/>
-      <c r="L12" s="139"/>
-      <c r="M12" s="139"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="138">
+      <c r="K12" s="141"/>
+      <c r="L12" s="141"/>
+      <c r="M12" s="141"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="143">
         <f t="array" aca="1" ref="O12" ca="1">SUM(R15:R25)+SUM(_xlfn._xlws.FILTER(Q15:Q25,R15:R25=""))+SUM(_xlfn._xlws.FILTER(P15:P25,(Q15:Q25="")*(R15:R25="")))</f>
         <v>17100</v>
       </c>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="140"/>
-      <c r="T12" s="138">
+      <c r="P12" s="141"/>
+      <c r="Q12" s="141"/>
+      <c r="R12" s="141"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="143">
         <f t="array" aca="1" ref="T12" ca="1">SUM(W15:W25)+SUM(_xlfn._xlws.FILTER(V15:V25,W15:W25=""))+SUM(_xlfn._xlws.FILTER(U15:U25,(V15:V25="")*(W15:W25="")))</f>
         <v>79073</v>
       </c>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="140"/>
-      <c r="Y12" s="138">
+      <c r="U12" s="141"/>
+      <c r="V12" s="141"/>
+      <c r="W12" s="141"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="143">
         <f t="array" aca="1" ref="Y12" ca="1">SUM(AB15:AB25)+SUM(_xlfn._xlws.FILTER(AA15:AA25,AB15:AB25=""))+SUM(_xlfn._xlws.FILTER(Z15:Z25,(AA15:AA25="")*(AB15:AB25="")))</f>
         <v>-2928.4444444444453</v>
       </c>
-      <c r="Z12" s="139"/>
-      <c r="AA12" s="139"/>
-      <c r="AB12" s="139"/>
-      <c r="AC12" s="140"/>
-      <c r="AD12" s="138">
+      <c r="Z12" s="141"/>
+      <c r="AA12" s="141"/>
+      <c r="AB12" s="141"/>
+      <c r="AC12" s="142"/>
+      <c r="AD12" s="143">
         <f t="array" aca="1" ref="AD12" ca="1">SUM(AG15:AG25)+SUM(_xlfn._xlws.FILTER(AF15:AF25,AG15:AG25=""))+SUM(_xlfn._xlws.FILTER(AE15:AE25,(AF15:AF25="")*(AG15:AG25="")))</f>
         <v>74786.555555555562</v>
       </c>
-      <c r="AE12" s="139"/>
-      <c r="AF12" s="139"/>
-      <c r="AG12" s="139"/>
-      <c r="AH12" s="140"/>
-      <c r="AI12" s="138">
+      <c r="AE12" s="141"/>
+      <c r="AF12" s="141"/>
+      <c r="AG12" s="141"/>
+      <c r="AH12" s="142"/>
+      <c r="AI12" s="143">
         <f t="array" aca="1" ref="AI12" ca="1">SUM(AL15:AL25)+SUM(_xlfn._xlws.FILTER(AK15:AK25,AL15:AL25=""))+SUM(_xlfn._xlws.FILTER(AJ15:AJ25,(AK15:AK25="")*(AL15:AL25="")))</f>
         <v>16094.555555555555</v>
       </c>
-      <c r="AJ12" s="139"/>
-      <c r="AK12" s="139"/>
-      <c r="AL12" s="139"/>
-      <c r="AM12" s="140"/>
-      <c r="AN12" s="138">
+      <c r="AJ12" s="141"/>
+      <c r="AK12" s="141"/>
+      <c r="AL12" s="141"/>
+      <c r="AM12" s="142"/>
+      <c r="AN12" s="143">
         <f t="array" aca="1" ref="AN12" ca="1">SUM(AQ15:AQ25)+SUM(_xlfn._xlws.FILTER(AP15:AP25,AQ15:AQ25=""))+SUM(_xlfn._xlws.FILTER(AO15:AO25,(AP15:AP25="")*(AQ15:AQ25="")))</f>
         <v>-38708.444444444445</v>
       </c>
-      <c r="AO12" s="139"/>
-      <c r="AP12" s="139"/>
-      <c r="AQ12" s="139"/>
-      <c r="AR12" s="140"/>
-      <c r="AS12" s="138">
+      <c r="AO12" s="141"/>
+      <c r="AP12" s="141"/>
+      <c r="AQ12" s="141"/>
+      <c r="AR12" s="142"/>
+      <c r="AS12" s="143">
         <f t="array" aca="1" ref="AS12" ca="1">SUM(AV15:AV25)+SUM(_xlfn._xlws.FILTER(AU15:AU25,AV15:AV25=""))+SUM(_xlfn._xlws.FILTER(AT15:AT25,(AU15:AU25="")*(AV15:AV25="")))</f>
         <v>-36735.944444444445</v>
       </c>
-      <c r="AT12" s="139"/>
-      <c r="AU12" s="139"/>
-      <c r="AV12" s="139"/>
-      <c r="AW12" s="140"/>
-      <c r="AX12" s="138">
+      <c r="AT12" s="141"/>
+      <c r="AU12" s="141"/>
+      <c r="AV12" s="141"/>
+      <c r="AW12" s="142"/>
+      <c r="AX12" s="143">
         <f t="array" aca="1" ref="AX12" ca="1">SUM(BA15:BA25)+SUM(_xlfn._xlws.FILTER(AZ15:AZ25,BA15:BA25=""))+SUM(_xlfn._xlws.FILTER(AY15:AY25,(AZ15:AZ25="")*(BA15:BA25="")))</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="AY12" s="139"/>
-      <c r="AZ12" s="139"/>
-      <c r="BA12" s="139"/>
-      <c r="BB12" s="140"/>
-      <c r="BC12" s="138">
+      <c r="AY12" s="141"/>
+      <c r="AZ12" s="141"/>
+      <c r="BA12" s="141"/>
+      <c r="BB12" s="142"/>
+      <c r="BC12" s="143">
         <f t="array" aca="1" ref="BC12" ca="1">SUM(BF15:BF25)+SUM(_xlfn._xlws.FILTER(BE15:BE25,BF15:BF25=""))+SUM(_xlfn._xlws.FILTER(BD15:BD25,(BE15:BE25="")*(BF15:BF25="")))</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BD12" s="139"/>
-      <c r="BE12" s="139"/>
-      <c r="BF12" s="139"/>
-      <c r="BG12" s="140"/>
-      <c r="BH12" s="138">
+      <c r="BD12" s="141"/>
+      <c r="BE12" s="141"/>
+      <c r="BF12" s="141"/>
+      <c r="BG12" s="142"/>
+      <c r="BH12" s="143">
         <f t="array" aca="1" ref="BH12" ca="1">SUM(BK15:BK25)+SUM(_xlfn._xlws.FILTER(BJ15:BJ25,BK15:BK25=""))+SUM(_xlfn._xlws.FILTER(BI15:BI25,(BJ15:BJ25="")*(BK15:BK25="")))</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BI12" s="139"/>
-      <c r="BJ12" s="139"/>
-      <c r="BK12" s="139"/>
-      <c r="BL12" s="140"/>
-      <c r="BM12" s="138">
+      <c r="BI12" s="141"/>
+      <c r="BJ12" s="141"/>
+      <c r="BK12" s="141"/>
+      <c r="BL12" s="142"/>
+      <c r="BM12" s="143">
         <f t="array" aca="1" ref="BM12" ca="1">SUM(BP15:BP25)+SUM(_xlfn._xlws.FILTER(BO15:BO25,BP15:BP25=""))+SUM(_xlfn._xlws.FILTER(BN15:BN25,(BO15:BO25="")*(BP15:BP25="")))</f>
         <v>-39135.944444444445</v>
       </c>
-      <c r="BN12" s="139"/>
-      <c r="BO12" s="139"/>
-      <c r="BP12" s="139"/>
-      <c r="BQ12" s="140"/>
+      <c r="BN12" s="141"/>
+      <c r="BO12" s="141"/>
+      <c r="BP12" s="141"/>
+      <c r="BQ12" s="142"/>
       <c r="BR12" s="21"/>
       <c r="BS12" s="22"/>
     </row>
@@ -2594,90 +2594,90 @@
         <v>22</v>
       </c>
       <c r="I13" s="146"/>
-      <c r="J13" s="142">
+      <c r="J13" s="147">
         <v>45688</v>
       </c>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="141" t="s">
+      <c r="K13" s="141"/>
+      <c r="L13" s="141"/>
+      <c r="M13" s="141"/>
+      <c r="N13" s="141"/>
+      <c r="O13" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="140"/>
-      <c r="T13" s="141">
+      <c r="P13" s="141"/>
+      <c r="Q13" s="141"/>
+      <c r="R13" s="141"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="140">
         <v>45747</v>
       </c>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="140"/>
-      <c r="Y13" s="141">
+      <c r="U13" s="141"/>
+      <c r="V13" s="141"/>
+      <c r="W13" s="141"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="140">
         <v>45777</v>
       </c>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="139"/>
-      <c r="AC13" s="140"/>
-      <c r="AD13" s="141">
+      <c r="Z13" s="141"/>
+      <c r="AA13" s="141"/>
+      <c r="AB13" s="141"/>
+      <c r="AC13" s="142"/>
+      <c r="AD13" s="140">
         <v>45808</v>
       </c>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="139"/>
-      <c r="AH13" s="140"/>
-      <c r="AI13" s="141">
+      <c r="AE13" s="141"/>
+      <c r="AF13" s="141"/>
+      <c r="AG13" s="141"/>
+      <c r="AH13" s="142"/>
+      <c r="AI13" s="140">
         <v>45838</v>
       </c>
-      <c r="AJ13" s="139"/>
-      <c r="AK13" s="139"/>
-      <c r="AL13" s="139"/>
-      <c r="AM13" s="140"/>
-      <c r="AN13" s="141">
+      <c r="AJ13" s="141"/>
+      <c r="AK13" s="141"/>
+      <c r="AL13" s="141"/>
+      <c r="AM13" s="142"/>
+      <c r="AN13" s="140">
         <v>45869</v>
       </c>
-      <c r="AO13" s="139"/>
-      <c r="AP13" s="139"/>
-      <c r="AQ13" s="139"/>
-      <c r="AR13" s="140"/>
-      <c r="AS13" s="141">
+      <c r="AO13" s="141"/>
+      <c r="AP13" s="141"/>
+      <c r="AQ13" s="141"/>
+      <c r="AR13" s="142"/>
+      <c r="AS13" s="140">
         <v>45900</v>
       </c>
-      <c r="AT13" s="139"/>
-      <c r="AU13" s="139"/>
-      <c r="AV13" s="139"/>
-      <c r="AW13" s="140"/>
-      <c r="AX13" s="141">
+      <c r="AT13" s="141"/>
+      <c r="AU13" s="141"/>
+      <c r="AV13" s="141"/>
+      <c r="AW13" s="142"/>
+      <c r="AX13" s="140">
         <v>45930</v>
       </c>
-      <c r="AY13" s="139"/>
-      <c r="AZ13" s="139"/>
-      <c r="BA13" s="139"/>
-      <c r="BB13" s="140"/>
-      <c r="BC13" s="141">
+      <c r="AY13" s="141"/>
+      <c r="AZ13" s="141"/>
+      <c r="BA13" s="141"/>
+      <c r="BB13" s="142"/>
+      <c r="BC13" s="140">
         <v>45961</v>
       </c>
-      <c r="BD13" s="139"/>
-      <c r="BE13" s="139"/>
-      <c r="BF13" s="139"/>
-      <c r="BG13" s="140"/>
-      <c r="BH13" s="141">
+      <c r="BD13" s="141"/>
+      <c r="BE13" s="141"/>
+      <c r="BF13" s="141"/>
+      <c r="BG13" s="142"/>
+      <c r="BH13" s="140">
         <v>45991</v>
       </c>
-      <c r="BI13" s="139"/>
-      <c r="BJ13" s="139"/>
-      <c r="BK13" s="139"/>
-      <c r="BL13" s="140"/>
-      <c r="BM13" s="141">
+      <c r="BI13" s="141"/>
+      <c r="BJ13" s="141"/>
+      <c r="BK13" s="141"/>
+      <c r="BL13" s="142"/>
+      <c r="BM13" s="140">
         <v>46022</v>
       </c>
-      <c r="BN13" s="139"/>
-      <c r="BO13" s="139"/>
-      <c r="BP13" s="139"/>
-      <c r="BQ13" s="140"/>
+      <c r="BN13" s="141"/>
+      <c r="BO13" s="141"/>
+      <c r="BP13" s="141"/>
+      <c r="BQ13" s="142"/>
       <c r="BR13" s="24">
         <f>SUM(BR15:BR24)</f>
         <v>352223.5</v>
@@ -4358,13 +4358,20 @@
   </sheetData>
   <autoFilter ref="B14:B20" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="39">
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="AS13:AW13"/>
-    <mergeCell ref="BC13:BG13"/>
-    <mergeCell ref="Y12:AC12"/>
-    <mergeCell ref="AI12:AM12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="AN13:AR13"/>
+    <mergeCell ref="BM12:BQ12"/>
+    <mergeCell ref="BC11:BG11"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="BM11:BQ11"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="BH12:BL12"/>
+    <mergeCell ref="AX11:BB11"/>
+    <mergeCell ref="AS12:AW12"/>
+    <mergeCell ref="AI11:AM11"/>
+    <mergeCell ref="BM13:BQ13"/>
+    <mergeCell ref="BH13:BL13"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="BH11:BL11"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="T12:X12"/>
     <mergeCell ref="J11:N11"/>
@@ -4381,22 +4388,15 @@
     <mergeCell ref="O13:S13"/>
     <mergeCell ref="T13:X13"/>
     <mergeCell ref="O12:S12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="AS13:AW13"/>
+    <mergeCell ref="BC13:BG13"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="AI12:AM12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="AN13:AR13"/>
     <mergeCell ref="AD12:AH12"/>
     <mergeCell ref="AI13:AM13"/>
-    <mergeCell ref="BM12:BQ12"/>
-    <mergeCell ref="BC11:BG11"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="BM11:BQ11"/>
-    <mergeCell ref="AD13:AH13"/>
-    <mergeCell ref="Y11:AC11"/>
-    <mergeCell ref="BH12:BL12"/>
-    <mergeCell ref="AX11:BB11"/>
-    <mergeCell ref="AS12:AW12"/>
-    <mergeCell ref="AI11:AM11"/>
-    <mergeCell ref="BM13:BQ13"/>
-    <mergeCell ref="BH13:BL13"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="BH11:BL11"/>
   </mergeCells>
   <conditionalFormatting sqref="M15:M24 R15:R24 W15:W24 AB15:AB24 AG15:AG24 AL15:AL24 AQ15:AQ24 AV15:AV24 BA15:BA24 BF15:BF24 BK15:BK24 BP15:BP24">
     <cfRule type="expression" dxfId="7" priority="8">
@@ -5222,7 +5222,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>34040</v>
       </c>
     </row>
-    <row r="4" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>62210</v>
       </c>
     </row>
-    <row r="6" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>58648</v>
       </c>
     </row>
-    <row r="8" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -6762,7 +6762,7 @@
         <v>-18462</v>
       </c>
     </row>
-    <row r="13" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>-22813.72</v>
       </c>
     </row>
-    <row r="14" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>19294.5</v>
       </c>
     </row>
-    <row r="15" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>18112</v>
       </c>
     </row>
-    <row r="20" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>20960</v>
       </c>
     </row>
-    <row r="26" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>-18502</v>
       </c>
     </row>
-    <row r="31" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>85</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>-19294.5</v>
       </c>
     </row>
-    <row r="32" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>85</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="37" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>98592</v>
       </c>
     </row>
-    <row r="41" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>-20952.78</v>
       </c>
     </row>
-    <row r="42" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>57824</v>
       </c>
     </row>
-    <row r="45" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>-13632.5</v>
       </c>
     </row>
-    <row r="46" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>13632.5</v>
       </c>
     </row>
-    <row r="47" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>-60224</v>
       </c>
     </row>
-    <row r="49" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>-14060</v>
       </c>
     </row>
-    <row r="50" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>38368</v>
       </c>
     </row>
-    <row r="52" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>85</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>60224</v>
       </c>
     </row>
-    <row r="55" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>85</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>-30922.5</v>
       </c>
     </row>
-    <row r="56" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>85</v>
       </c>
@@ -12924,9 +12924,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L56" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="11">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Reclass"/>
+        <filter val="9500879389"/>
       </filters>
     </filterColumn>
   </autoFilter>
